--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-003_テーブル設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-003_テーブル設計書.xlsx
@@ -97,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9D18E"/>
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
+        <fgColor rgb="00A9D18E"/>
       </patternFill>
     </fill>
     <fill>
@@ -202,13 +202,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -679,7 +679,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-TBL-01〜09（テーブル詳細設計書）／ backend/schema.sql</t>
+          <t>KF-DD-TBL-01〜09（テーブル詳細設計書）／ backend/src/main/resources/db/migration/V1__init_schema.sql</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G29"/>
+  <dimension ref="A2:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -746,7 +746,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>休暇種別 leave_types（11 件。schema.sql の INSERT）</t>
+          <t>休暇種別 leave_types（11 件。V1__init_schema.sql の INSERT）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -1154,7 +1154,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>部署 departments（3 件。schema.sql の INSERT）</t>
+          <t>部署 departments（5 件。V1__init_schema.sql の INSERT）</t>
         </is>
       </c>
       <c r="B17" s="9" t="n"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>人事部</t>
+          <t>管理部</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>営業部</t>
+          <t>システム開発事業部</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>開発部</t>
+          <t>ソリューション事業部</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr"/>
@@ -1226,197 +1226,341 @@
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>開発用ユーザー users（4 件。schema.sql ではなく DevDataInitializer が userRepository.count() = 0 のときだけ作成。本番では使用しない）</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>SAP事業部</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>クラウド基盤サービス部</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>開発用ユーザー users（100 件。V1 ではなく DevDataInitializer が userRepository.count() = 0 かつ seed-password 設定時のみ作成。本番では使用しない）</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>メール</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>氏名 / ロール</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>部署</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>上長</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="48.5" customHeight="1">
-      <c r="A25" s="6" t="n">
+      <c r="G26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="63" customHeight="1">
+      <c r="A27" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>admin@example.com</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>人事 管理者 / ADMIN</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>人事部</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>全員 hire_date=2024-04-01、status=ACTIVE、パスワードは設定値を BCrypt 化（$2a$10$...）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="48.5" customHeight="1">
-      <c r="A26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>manager@example.com</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>佐藤 一郎 / MANAGER</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>営業部</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>全員 hire_date=2024-04-01、status=ACTIVE、パスワードは設定値を BCrypt 化（$2a$10$...）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="48.5" customHeight="1">
-      <c r="A27" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>taro@example.com</t>
+          <t>admin@example.com 、adm002@example.com</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>山田 太郎 / EMPLOYEE</t>
+          <t>人事 管理者 ほか / ADMIN（2 名）</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>営業部</t>
+          <t>管理部</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>佐藤 一郎</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>全員 hire_date=2024-04-01、status=ACTIVE、パスワードは設定値を BCrypt 化（$2a$10$...）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48.5" customHeight="1">
+          <t>全員 hire_date=2024-04-01 相当、status=ACTIVE、must_change_password=FALSE、パスワードは設定値を BCrypt 化（$2a$10$...）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>hanako@example.com</t>
+          <t>adm003@example.com</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>鈴木 花子 / EMPLOYEE</t>
+          <t>（架空氏名）/ MANAGER</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>営業部</t>
+          <t>管理部</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>佐藤 一郎</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>全員 hire_date=2024-04-01、status=ACTIVE、パスワードは設定値を BCrypt 化（$2a$10$...）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>adm004〜adm010@example.com</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ EMPLOYEE（7 名）</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>管理部</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>adm003</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>manager@example.com 、dev002@example.com</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>佐藤 一郎 ほか / MANAGER（2 名）</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>システム開発事業部</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="63" customHeight="1">
+      <c r="A31" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>taro@example.com 、hanako@example.com 、dev005〜dev030@example.com</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>山田 太郎、鈴木 花子 ほか / EMPLOYEE（28 名）</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>システム開発事業部</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>manager@ / dev002@（番号の偶奇で振分け）</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>sol001〜sol025@example.com</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 23</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>ソリューション事業部</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>sol001 / sol002</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>sap001〜sap020@example.com</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 18</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>SAP事業部</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>sap001 / sap002</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>cld001〜cld015@example.com</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 13</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>クラウド基盤サービス部</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>cld001 / cld002</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>本番の初期管理者は BootstrapAdminInitializer が users が空かつ設定が揃うときだけ 1 名作成する（部署=管理部、must_change_password=TRUE）。</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>その他の表（leave_balances / attendance_records / requests / approval_steps / holidays / notifications）の初期データは無い。祝日は管理者が ONL-016 で登録する。</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="10" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C24:D24"/>
+  <mergeCells count="15">
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
     <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="C31:D31"/>
     <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1455,7 +1599,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48.5" customHeight="1">
+    <row r="2" ht="63" customHeight="1">
       <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
@@ -1466,11 +1610,11 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>backend/schema.sql を開発者が手動実行して DB を作る。ファイルは先頭に DROP TABLE ... CASCADE を含み、再実行すると全データが消える（開発専用。課題 C-3）。Spring Boot 側は spring.jpa.hibernate.ddl-auto=validate とし、起動時に Entity と DB の型・列の整合を検証する（DDL を自動生成・変更させない）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48.5" customHeight="1">
+          <t>Flyway で管理する。backend/src/main/resources/db/migration/V1__init_schema.sql（DDL・トリガ・初期データ。DROP は含まない）をアプリ起動時に自動適用する。旧 backend/schema.sql（手動実行・先頭に DROP）は廃止（解消済み C-3）。Spring Boot 側は spring.jpa.hibernate.ddl-auto=validate とし、起動時に Entity と DB の型・列の整合を検証する（DDL を自動生成・変更させない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="63" customHeight="1">
       <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
@@ -1481,7 +1625,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>①空の DB を作成（運用接続用に ALTER DATABASE ... SET timezone TO 'Asia/Tokyo' を併用。課題 C-6）②psql -f backend/schema.sql（テーブル・索引・関数 set_updated_at・トリガ・初期データ）③アプリ起動（Hikari の connection-init-sql で JST に固定。ddl-auto=validate が通ることを確認）④開発のみ DevDataInitializer が初期ユーザーを作る。</t>
+          <t>①空の DB を作成（運用接続用に ALTER DATABASE ... SET timezone TO 'Asia/Tokyo' を併用。課題 C-6）②アプリ（または docker compose up -d --build）を起動すると Flyway が V1 を適用（テーブル・索引・関数 set_updated_at・トリガ・初期データ）③Hikari の connection-init-sql で JST に固定され、ddl-auto=validate が通ることを確認④開発のみ DevDataInitializer が開発用ユーザーを、本番は BootstrapAdminInitializer が初期管理者を作る。</t>
         </is>
       </c>
     </row>
@@ -1496,22 +1640,22 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>列・制約・索引の変更は schema.sql を直接書き換えず、ALTER 文のスクリプトを別に作成し、本番適用前に件数・重複の確認 SQL（各テーブル詳細設計書 10章）で既存データが新制約を満たすことを確認する。schema.sql 自体は適用後に最新の定義へ更新する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>V1 は適用後に編集しない（Flyway がチェックサムを検証し、編集すると起動に失敗する）。列・制約・索引の変更は V2__&lt;内容&gt;.sql のように新しいファイルを追加する。本番適用前に件数・重複の確認 SQL（各テーブル詳細設計書 10章）で既存データが新制約を満たすことを確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48.5" customHeight="1">
       <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>将来（Flyway 検討）</t>
+          <t>既存の開発 DB</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Flyway を導入し、現行 schema.sql（DROP 無し）を V1__baseline.sql、初期データを R__seed または V2__seed.sql に分割する。以降の変更は V3__ 以降の増分とする。ddl-auto=validate は継続。既存環境には baselineOnMigrate で取り込む。</t>
+          <t>旧 schema.sql で作った DB は spring.flyway.baseline-on-migrate=true・baseline-version=1 により V1 適用済みとして取り込まれる。ただし V1 に含まれる新しい列（users の 4 列）は追加されず、ddl-auto=validate で起動に失敗する。backend/db/reset-dev.sql（DROP SCHEMA public CASCADE; CREATE SCHEMA public;）で作り直す。本番では実行しない。</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1685,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>各詳細設計書 3.4 の推奨 DDL（採否は課題一覧の優先度で決める）：idx_lb_user 廃止（LB-6）、ck_users_email_lower（U-4）、requests / leave_balances / attendance_records の CHECK、notifications の ck_notif_type・ck_notif_request（N-3）と索引置換（N-2）。解消済みの項目（updated_at トリガ・notifications の type/request_id・uq_leave_balances_1・idx_att_user_date 削除）は schema.sql v2.0 に反映済み。</t>
+          <t>各詳細設計書 3.4 の推奨 DDL（採否は課題一覧の優先度で決める）：idx_lb_user 廃止（LB-6）、ck_users_email_lower（U-4）、requests / leave_balances / attendance_records の CHECK、notifications の ck_notif_type・ck_notif_request（N-3）と索引置換（N-2）。解消済みの項目（updated_at トリガ・notifications の type/request_id・uq_leave_balances_1・idx_att_user_date 削除）は V1__init_schema.sql に反映済み。</t>
         </is>
       </c>
     </row>
@@ -1635,72 +1779,72 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="63" customHeight="1">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>C-3</t>
+          <t>C-4</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
+          <t>PK 制約名が未指定で命名規約と不統一</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
+          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
+          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
+          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="63" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>C-5</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>業務ルールの CHECK 制約が少ない</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
           <t>中</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>C-4</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>PK 制約名が未指定で命名規約と不統一</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -1712,27 +1856,27 @@
     <row r="6" ht="63" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>C-5</t>
+          <t>C-6</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>業務ルールの CHECK 制約が少ない</t>
+          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1746,178 +1890,178 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="63" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>C-6</t>
+          <t>U-2</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
+          <t>上長の自己参照・循環を DB で防げない</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>users.manager_id は自己参照 FK。manager_id = id や循環（A→B→A）は ONL-014 のアプリ判定のみ。</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
+          <t>手動 SQL で循環を作ると承認ルートが成立しない。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
+          <t>CHECK (manager_id IS NULL OR manager_id &lt;&gt; id) を追加。循環は 10章の再帰 CTE で定期検査。</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="63" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>U-4</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>email の小文字化を DB が強制しない</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>保存時の小文字化はアプリの責務で、DB に CHECK も LOWER(email) の一意索引も無い。アプリを経由しない手動 SQL や将来の別入口では大文字混じりのメールが入り、uq_users_1 では大文字小文字違いの重複を防げない。</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>大文字混じりのメールはログインに一致しなくなる（検索は小文字）。</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>CHECK (email = LOWER(email))（ck_users_email_lower）を追加。事前に 10章『大文字・前後空白を含むメール』が 0 行であることを確認。</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="63" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>departments に UNIQUE が無く、管理機能も無い</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>部署名の重複を DB が許す。オンライン処理に部署の登録・変更 API が無い（ONL-014 は R のみ）。初期 5 部署は V1__init_schema.sql の INSERT のみ。部署名変更は過去の申請・集計にも現在名で表示される（ONL-007）。</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>部署追加・改名は SQL 直接実行になる。重複部署の混入を防げない。</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>uq_departments_1 (name) を追加。部署管理 ONL の追加を検討（無効化用 is_active 列も）。</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>U-2</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>上長の自己参照・循環を DB で防げない</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>users.manager_id は自己参照 FK。manager_id = id や循環（A→B→A）は ONL-014 のアプリ判定のみ。</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>手動 SQL で循環を作ると承認ルートが成立しない。</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>CHECK (manager_id IS NULL OR manager_id &lt;&gt; id) を追加。循環は 10章の再帰 CTE で定期検査。</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48.5" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>U-3</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>ログイン失敗回数・パスワード変更日などの列が無い</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>ONL-001「未対応（今後）」：連続失敗ロック・ログイン履歴・トークン失効。ONL-014「初回ログイン時のパスワード強制変更」も未対応。</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>総当たり攻撃対策・パスワード期限管理ができない。無効化・ロール変更が発行済み JWT（最大 8 時間）に即時反映されない。</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>必要時に failed_login_count / locked_until / password_changed_at / token_version を追加（要 ALTER とマイグレーション）。</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>users</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="63" customHeight="1">
+          <t>departments</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48.5" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>U-4</t>
+          <t>LT-1</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>email の小文字化を DB が強制しない</t>
+          <t>leave_types.max_days_rule が NULL 可</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>保存時の小文字化はアプリ（EmailNormalizer）の責務で、DB に CHECK も LOWER(email) の一意索引も無い。アプリを経由しない手動 SQL や将来の別入口では大文字混じりのメールが入り、uq_users_1 では大文字小文字違いの重複を防げない。</t>
+          <t>列は NULL 許可で ck_lt_rule も NULL を通す（SQL の CHECK は NULL で真）。KF-BD-005 と ONL-015 では必須（LIMITED / UNLIMITED）。</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>大文字混じりのメールはログインに一致しなくなる（検索は小文字）。</t>
+          <t>NULL の種別は LIMITED でも UNLIMITED でもなく、ONL-005 の残日数判定が不定になる。</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>CHECK (email = LOWER(email))（ck_users_email_lower）を追加。事前に 10章『大文字・前後空白を含むメール』が 0 行であることを確認。</t>
+          <t>NOT NULL 化（既存 11 件は設定済み）。</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>users</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="63" customHeight="1">
+          <t>leave_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48.5" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>LT-2</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>departments に UNIQUE が無く、管理機能も無い</t>
+          <t>年次有給休暇を名称で特定している</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>部署名の重複を DB が許す。オンライン処理に部署の登録・変更 API が無い（ONL-014 は R のみ）。初期 3 部署は schema.sql の INSERT のみ。部署名変更は過去の申請・集計にも現在名で表示される（ONL-007）。</t>
+          <t>ONL-013 は findByName('年次有給休暇') で年休を判定。名称変更は ONL-015 が E-016 で拒否するが DB は保護しない。表示順の列も無く id 昇順（ONL-021）。</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>部署追加・改名は SQL 直接実行になる。重複部署の混入を防げない。</t>
+          <t>SQL 等で改名すると年休判定・年 5 日義務・BAT-001/002 が働かなくなる。</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>uq_departments_1 (name) を追加。部署管理 ONL の追加を検討（無効化用 is_active 列も）。</t>
+          <t>code 列（例 ANNUAL_LEAVE）追加、または name 変更を禁止するトリガ。display_order 列の追加を検討。</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1927,108 +2071,108 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>departments</t>
+          <t>leave_types</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48.5" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>LT-1</t>
+          <t>LT-3</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>leave_types.max_days_rule が NULL 可</t>
+          <t>日数上限（子の看護・介護休暇、介護休業）は leave_balances の付与で管理</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>列は NULL 許可で ck_lt_rule も NULL を通す（SQL の CHECK は NULL で真）。KF-BD-005 と ONL-015 では必須（LIMITED / UNLIMITED）。</t>
+          <t>leave_types には上限日数を持たず、LIMITED 種別は管理者の付与（ONL-017）が無いと残 0 日になる。BAT-001 が自動付与するのは年次有給休暇のみ。</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>NULL の種別は LIMITED でも UNLIMITED でもなく、ONL-005 の残日数判定が不定になる。</t>
+          <t>付与漏れがあると申請時に E-004（残日数不足）となる。運用ルールが DB から読み取れない。</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>NOT NULL 化（既存 11 件は設定済み）。</t>
+          <t>default_days（既定付与日数）列の追加、または付与運用手順を運用設計書に明記。</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>leave_types, leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>LB-2</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>残日数の整合 CHECK が無い</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>granted_days &gt; 0、used_days &gt;= 0、used_days &lt;= granted_days、expires_on &gt; granted_on を DB が保証しない。</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>consume/restore のバグや手動更新で used_days が付与を超える・負になる。</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>CHECK 4 本を追加（ck_lb_days, ck_lb_period）。</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>leave_types</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48.5" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>LT-2</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>年次有給休暇を名称で特定している</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>ONL-013 は findByName('年次有給休暇') で年休を判定。名称変更は ONL-015 が E-016 で拒否するが DB は保護しない。表示順の列も無く id 昇順（ONL-021）。</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>SQL 等で改名すると年休判定・年 5 日義務・BAT-001/002 が働かなくなる。</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>code 列（例 ANNUAL_LEAVE）追加、または name 変更を禁止するトリガ。display_order 列の追加を検討。</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>leave_types</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48.5" customHeight="1">
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>LT-3</t>
+          <t>LB-4</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>日数上限（子の看護・介護休暇、介護休業）は leave_balances の付与で管理</t>
+          <t>消化の内訳が残らない</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>leave_types には上限日数を持たず、LIMITED 種別は管理者の付与（ONL-017）が無いと残 0 日になる。BAT-001 が自動付与するのは年次有給休暇のみ。</t>
+          <t>consume は FIFO で複数の付与行から引くが、どの行から何日引いたかを記録しない（ONL-013 既知の制約）。</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>付与漏れがあると申請時に E-004（残日数不足）となる。運用ルールが DB から読み取れない。</t>
+          <t>取消（restore）時に元の行へ正確に戻せない。監査証跡が無い。</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>default_days（既定付与日数）列の追加、または付与運用手順を運用設計書に明記。</t>
+          <t>leave_balance_usages（request_id, leave_balance_id, days）の追加を検討。</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -2038,145 +2182,145 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>leave_types, leave_balances</t>
+          <t>leave_balances</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>LB-2</t>
+          <t>LB-5</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>残日数の整合 CHECK が無い</t>
+          <t>付与・調整の理由を保存する列が無い</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>granted_days &gt; 0、used_days &gt;= 0、used_days &lt;= granted_days、expires_on &gt; granted_on を DB が保証しない。</t>
+          <t>ONL-017 D-2：note は通知本文に使うだけで DB に保存しない。</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>consume/restore のバグや手動更新で used_days が付与を超える・負になる。</t>
+          <t>調整履歴で理由を追えない。</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>CHECK 4 本を追加（ck_lb_days, ck_lb_period）。</t>
+          <t>note VARCHAR(200) 列の追加（ONL-017 将来課題）。</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="63" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>LB-6</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>idx_lb_user が uq_leave_balances_1 に包含されて冗長</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>uq_leave_balances_1 (user_id, leave_type_id, granted_on) の先頭 2 列が idx_lb_user (user_id, leave_type_id) と同一で、残日数合計・FIFO 消化・付与履歴の検索はどちらでも賄える。</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>書込み時の索引更新とストレージが無駄（影響は小さい）。</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>DROP INDEX idx_lb_user;</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48.5" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>勤怠値の整合 CHECK が無い</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>clock_out &gt;= clock_in、work_minutes &gt;= 0、overtime_minutes &gt;= 0、clock_out があれば clock_in も必須、を DB が保証しない。</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>打刻修正（ONL-010）や手動更新で退勤が出勤より前、負の時間などを保存できる。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>CHECK を追加（ck_att_time, ck_att_minutes）。</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>LB-4</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>消化の内訳が残らない</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>consume は FIFO で複数の付与行から引くが、どの行から何日引いたかを記録しない（ONL-013 既知の制約）。</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>取消（restore）時に元の行へ正確に戻せない。監査証跡が無い。</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>leave_balance_usages（request_id, leave_balance_id, days）の追加を検討。</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>LB-5</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>付与・調整の理由を保存する列が無い</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>ONL-017 D-2：note は通知本文に使うだけで DB に保存しない。</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>調整履歴で理由を追えない。</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>note VARCHAR(200) 列の追加（ONL-017 将来課題）。</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>leave_balances</t>
+          <t>attendance_records</t>
         </is>
       </c>
     </row>
     <row r="18" ht="63" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>LB-6</t>
+          <t>A-3</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>idx_lb_user が uq_leave_balances_1 に包含されて冗長</t>
+          <t>日跨ぎ勤務・休憩・修正履歴に非対応</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>uq_leave_balances_1 (user_id, leave_type_id, granted_on) の先頭 2 列が idx_lb_user (user_id, leave_type_id) と同一で、残日数合計・FIFO 消化・付与履歴の検索はどちらでも賄える。</t>
+          <t>ONL-003：日跨ぎ勤務は未対応（前日出勤・未退勤は E-007）。休憩・所定労働時間の列が無く work_minutes の計算規則はアプリ内。ONL-010 の打刻修正は attendance_records を上書きし、修正前の値・修正者を残さない。</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>書込み時の索引更新とストレージが無駄（影響は小さい）。</t>
+          <t>夜勤・修正の監査ができない。work_minutes の再計算根拠が DB に無い。</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>DROP INDEX idx_lb_user;</t>
+          <t>break_minutes 列、attendance_record_audits（修正履歴）の追加を検討。</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -2186,108 +2330,108 @@
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48.5" customHeight="1">
+          <t>attendance_records</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="63" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>A-2</t>
+          <t>A-4</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>勤怠値の整合 CHECK が無い</t>
+          <t>月次集計は work_date 先頭の索引が無い</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>clock_out &gt;= clock_in、work_minutes &gt;= 0、overtime_minutes &gt;= 0、clock_out があれば clock_in も必須、を DB が保証しない。</t>
+          <t>ONL-018/020 の集計サブクエリは work_date BETWEEN のみで user_id を限定しない。idx は user_id 先頭のため使えず、期間で全件走査になる（300 名×約 22 日≒6,600 行/月、年 75,000 行までは問題なし）。</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>打刻修正（ONL-010）や手動更新で退勤が出勤より前、負の時間などを保存できる。</t>
+          <t>数年分（数十万行）に増えると月次集計が遅くなる。</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>CHECK を追加（ck_att_time, ck_att_minutes）。</t>
+          <t>必要になった時点で idx_att_work_date (work_date) を追加（現状は不要）。</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>attendance_records</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="77.5" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>R-2</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>requests の CHECK 不足（期間・段・種別別必須列）</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>start_date &lt;= end_date、current_step の範囲（0=下書き,1,2）、days &gt; 0、LEAVE 時の leave_type_id/unit/days 必須、CLOCK_CORRECTION 時の corrected_clock_in/out 必須、status と submitted_at の対応を DB が保証しない。current_step は NOT NULL だが DEFAULT も無い。</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>手動投入・将来の別入口で矛盾した申請が入る。</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>ck_req_period / ck_req_step / ck_req_days / ck_req_kind を追加（本書 3章の推奨 DDL）。</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>attendance_records</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="63" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>A-3</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>日跨ぎ勤務・休憩・修正履歴に非対応</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>ONL-003：日跨ぎ勤務は未対応（前日出勤・未退勤は E-007）。休憩・所定労働時間の列が無く work_minutes の計算規則はアプリ内。ONL-010 の打刻修正は attendance_records を上書きし、修正前の値・修正者を残さない。</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>夜勤・修正の監査ができない。work_minutes の再計算根拠が DB に無い。</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>break_minutes 列、attendance_record_audits（修正履歴）の追加を検討。</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>attendance_records</t>
+          <t>requests</t>
         </is>
       </c>
     </row>
     <row r="21" ht="63" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>A-4</t>
+          <t>R-3</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>月次集計は work_date 先頭の索引が無い</t>
+          <t>取下げ・差戻し等の実行日時・実行者を専用列に残せない</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>ONL-018/020 の集計サブクエリは work_date BETWEEN のみで user_id を限定しない。idx は user_id 先頭のため使えず、期間で全件走査になる（300 名×約 22 日≒6,600 行/月、年 75,000 行までは問題なし）。</t>
+          <t>updated_at はトリガで信頼できるが、取下げ以外の更新でも更新されるため『取下げ日時』とは断定できない。取下げ者は申請者本人のみのため不要だが、承認履歴は approval_steps にのみ存在する。</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>数年分（数十万行）に増えると月次集計が遅くなる。</t>
+          <t>取下げ日時を厳密に出せない（最終更新日時で代用）。</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>必要になった時点で idx_att_work_date (work_date) を追加（現状は不要）。</t>
+          <t>必要なら withdrawn_at 列を追加。</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -2297,39 +2441,39 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>attendance_records</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="77.5" customHeight="1">
+          <t>requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48.5" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>R-2</t>
+          <t>R-4</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>requests の CHECK 不足（期間・段・種別別必須列）</t>
+          <t>楽観ロック用 version 列が無い</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>start_date &lt;= end_date、current_step の範囲（0=下書き,1,2）、days &gt; 0、LEAVE 時の leave_type_id/unit/days 必須、CLOCK_CORRECTION 時の corrected_clock_in/out 必須、status と submitted_at の対応を DB が保証しない。current_step は NOT NULL だが DEFAULT も無い。</t>
+          <t>@Version を使えず、requests 行の SELECT ... FOR UPDATE ＋ 状態条件付き UPDATE で排他している（ONL-010 決定事項）。</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>手動投入・将来の別入口で矛盾した申請が入る。</t>
+          <t>現方式で二重承認は防げるが、ロック待ちが発生する。他の更新経路（管理画面等）が増えると漏れやすい。</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>ck_req_period / ck_req_step / ck_req_days / ck_req_kind を追加（本書 3章の推奨 DDL）。</t>
+          <t>当面は現方式を維持。更新経路が増える時点で version BIGINT NOT NULL DEFAULT 0 を追加。</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -2341,27 +2485,27 @@
     <row r="23" ht="63" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>R-3</t>
+          <t>R-5</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>取下げ・差戻し等の実行日時・実行者を専用列に残せない</t>
+          <t>集計用の索引が無い</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>updated_at はトリガで信頼できるが、取下げ以外の更新でも更新されるため『取下げ日時』とは断定できない。取下げ者は申請者本人のみのため不要だが、承認履歴は approval_steps にのみ存在する。</t>
+          <t>ONL-018/020 の requests サブクエリは request_type='LEAVE' AND status='APPROVED' AND start_date BETWEEN（user_id 指定なし）で、user_id 先頭の idx_req_* が使えず全件走査（年 5,000 行までは問題なし）。</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>取下げ日時を厳密に出せない（最終更新日時で代用）。</t>
+          <t>数年分で月次集計が遅くなる可能性。</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>必要なら withdrawn_at 列を追加。</t>
+          <t>必要になった時点で (status, start_date) の部分索引を追加。</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2378,101 +2522,101 @@
     <row r="24" ht="48.5" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>R-4</t>
+          <t>R-6</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>楽観ロック用 version 列が無い</t>
+          <t>承認ルート確定後の上長変更・無効化への追従が無い</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>@Version を使えず、requests 行の SELECT ... FOR UPDATE ＋ 状態条件付き UPDATE で排他している（ONL-010 決定事項）。</t>
+          <t>承認ルート確定後に users.manager_id が変わっても approval_steps.approver_id は変わらない。1段目の上長が INACTIVE になった場合の代理承認は未対応（ONL-005/010）。</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>現方式で二重承認は防げるが、ロック待ちが発生する。他の更新経路（管理画面等）が増えると漏れやすい。</t>
+          <t>承認待ちのまま止まる申請が発生しうる。</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>当面は現方式を維持。更新経路が増える時点で version BIGINT NOT NULL DEFAULT 0 を追加。</t>
+          <t>承認者付替えの管理機能（ONL-014 将来課題）。10章 SQL「承認者が無効な待ち」で検出。</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
+          <t>requests, approval_steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48.5" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>R-7</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>下書き・差戻しの内容を更新する API が無い</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ONL-022 は提出（再提出）のみで、下書きの内容更新（PUT）は未定義。RETURNED の申請も内容を修正できず、直したい場合は取り下げて新規申請になる。</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>差戻しの目的（修正して再提出）を画面で果たせない。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>更新 API（PUT /api/requests/{id}）の追加（DRAFT / RETURNED のみ可）。</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
           <t>requests</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="63" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>R-5</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>集計用の索引が無い</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>ONL-018/020 の requests サブクエリは request_type='LEAVE' AND status='APPROVED' AND start_date BETWEEN（user_id 指定なし）で、user_id 先頭の idx_req_* が使えず全件走査（年 5,000 行までは問題なし）。</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>数年分で月次集計が遅くなる可能性。</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>必要になった時点で (status, start_date) の部分索引を追加。</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="48.5" customHeight="1">
+    <row r="26" ht="77.5" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>R-6</t>
+          <t>AS-1</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>承認ルート確定後の上長変更・無効化への追従が無い</t>
+          <t>WITHDRAWN 等の終了申請に WAITING のステップが残る</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>承認ルート確定後に users.manager_id が変わっても approval_steps.approver_id は変わらない。1段目の上長が INACTIVE になった場合の代理承認は未対応（ONL-005/010）。</t>
+          <t>ONL-008 は approval_steps を更新しない。ONL-011/012 の SQL は処理した 1 ステップのみ更新し、他段を更新しない。例：1段目で却下すると 2段目は WAITING のまま。</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>承認待ちのまま止まる申請が発生しうる。</t>
+          <t>approval_steps.status = 'WAITING' だけでは「処理待ち」を意味しない。必ず requests.status='PENDING' AND current_step = step_no と併用する（ONL-009 は実施済み）。集計・バッチで誤用しやすい。</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>承認者付替えの管理機能（ONL-014 将来課題）。10章 SQL「承認者が無効な待ち」で検出。</t>
+          <t>方針を明文化（現行の維持）。もしくは終端時に未処理ステップを CANCELLED 等へ更新（コード値追加）。</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -2482,71 +2626,71 @@
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>requests, approval_steps</t>
+          <t>approval_steps, requests</t>
         </is>
       </c>
     </row>
     <row r="27" ht="48.5" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>R-7</t>
+          <t>AS-2</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>下書き・差戻しの内容を更新する API が無い</t>
+          <t>ck_as_step が 1,2 固定で 3 段以上に拡張できず、整合 CHECK も無い</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>ONL-022 は提出（再提出）のみで、下書きの内容更新（PUT）は未定義。RETURNED の申請も内容を修正できず、直したい場合は取り下げて新規申請になる。</t>
+          <t>step_no IN (1,2) は固定。status='WAITING' ⇔ acted_at IS NULL、WAITING 以外は acted_at が必須、といった整合を DB は保証しない。</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>差戻しの目的（修正して再提出）を画面で果たせない。</t>
+          <t>承認段数を増やすと DDL 変更が必要。acted_at 欠落データが入りうる。</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>更新 API（PUT /api/requests/{id}）の追加（DRAFT / RETURNED のみ可）。</t>
+          <t>ck_as_step を step_no BETWEEN 1 AND 9 等へ緩和するか現状維持を決定。ck_as_acted を追加。</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="77.5" customHeight="1">
+          <t>approval_steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="63" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>AS-1</t>
+          <t>AS-3</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>WITHDRAWN 等の終了申請に WAITING のステップが残る</t>
+          <t>再提出で差戻しコメントなどの承認履歴が失われる</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>ONL-008 は approval_steps を更新しない。ONL-011/012 の SQL は処理した 1 ステップのみ更新し、他段を更新しない。例：1段目で却下すると 2段目は WAITING のまま。</t>
+          <t>ONL-022 は再提出時に旧 approval_steps を全て DELETE して作り直す（uq(request_id, step_no) のため INSERT し直す）。差戻しコメント・処理者・処理日時を含む前回の履歴は DB に残らず、ONL-007 の承認履歴には再提出後のステップのみが出る。</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>approval_steps.status = 'WAITING' だけでは「処理待ち」を意味しない。必ず requests.status='PENDING' AND current_step = step_no と併用する（ONL-009 は実施済み）。集計・バッチで誤用しやすい。</t>
+          <t>承認履歴（コメント・処理者）の喪失。監査・紛争時に追えない。</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>方針を明文化（現行の維持）。もしくは終端時に未処理ステップを CANCELLED 等へ更新（コード値追加）。</t>
+          <t>approval_histories（ステップ処理の追記専用ログ）を追加するか、再提出ごとに submit_no を持たせる。</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -2563,27 +2707,27 @@
     <row r="29" ht="48.5" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>AS-2</t>
+          <t>AS-4</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>ck_as_step が 1,2 固定で 3 段以上に拡張できず、整合 CHECK も無い</t>
+          <t>approver_id の索引は 2段目（NULL）検索に最適でない</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>step_no IN (1,2) は固定。status='WAITING' ⇔ acted_at IS NULL、WAITING 以外は acted_at が必須、といった整合を DB は保証しない。</t>
+          <t>ONL-009 の承認待ち検索は (1段目 approver_id = 自分) OR (2段目 かつ ADMIN) の OR 条件で、idx_as_approver (approver_id, status) だけでは 2段目を絞り込めない。</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>承認段数を増やすと DDL 変更が必要。acted_at 欠落データが入りうる。</t>
+          <t>WAITING が累積すると走査が増える（年 10,000 行までは問題なし）。</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>ck_as_step を step_no BETWEEN 1 AND 9 等へ緩和するか現状維持を決定。ck_as_acted を追加。</t>
+          <t>(step_no, status) WHERE status='WAITING' の部分索引を追加。</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -2600,212 +2744,212 @@
     <row r="30" ht="63" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>AS-3</t>
+          <t>AS-5</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>再提出で差戻しコメントなどの承認履歴が失われる</t>
+          <t>ONL-022 規格が存在しない索引 idx_as_request を参照している</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>ONL-022 は再提出時に旧 approval_steps を全て DELETE して作り直す（uq(request_id, step_no) のため INSERT し直す）。差戻しコメント・処理者・処理日時を含む前回の履歴は DB に残らず、ONL-007 の承認履歴には再提出後のステップのみが出る。</t>
+          <t>ONL-022 の deleteByRequestId の備考に『idx_as_request（request_id）を利用』とあるが、V1__init_schema.sql に該当索引は無い。実際は uq_approval_steps_1 (request_id, step_no) の先頭列が使われる（追加索引は不要）。</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>承認履歴（コメント・処理者）の喪失。監査・紛争時に追えない。</t>
+          <t>設計書と DDL の不一致（実害なし）。</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>approval_histories（ステップ処理の追記専用ログ）を追加するか、再提出ごとに submit_no を持たせる。</t>
+          <t>ONL-022 規格の記載を uq_approval_steps_1 に修正する。</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>approval_steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="63" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>H-1</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>祝日は物理削除可で、誤削除・再計算の仕組みが無い</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ONL-016：祝日は物理削除。削除・追加は以後の申請の日数計算にのみ影響し、作成済み requests.days は再計算しない。2000-2099 の範囲制限は ONL-016 の入力チェックのみで DB に CHECK が無い。</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>日数が祝日の追加漏れ時点の値で確定する。履歴が残らない。</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>祝日の年次一括登録手順（内閣府 CSV 取込）を運用に定義。ck_holiday_range を追加。</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>H-2</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>祝日と会社休日を区別できない</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>KF-DD-003 は「祝日・会社休日」だが種別列が無く name で区別する。</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>会社休日のみ・祝日のみの抽出ができない。</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>kind 列（NATIONAL / COMPANY）追加を検討。</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="77.5" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>N-2</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>通知の保持・削除方針が無く、取得索引も最適でない</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>年 20,000 件増加。ONL-019 は最新 50 件のみ取得し、画面は先頭 5 件。idx_notif_user (user_id, is_read) の is_read を使う SELECT が無く、一覧の ORDER BY created_at DESC, id DESC のソートが残る。月次の重複確認（user_id, type, created_at 範囲）も user_id のみで絞る。</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>数年で行数が増え続ける。1 ユーザーの全通知をソートして上位 50 件を取る無駄が出る。</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>保持 1 年を超える既読通知の削除バッチを追加。索引を (user_id, created_at DESC, id DESC) へ変更。</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
           <t>中</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps, requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="48.5" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>AS-4</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>approver_id の索引は 2段目（NULL）検索に最適でない</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>ONL-009 の承認待ち検索は (1段目 approver_id = 自分) OR (2段目 かつ ADMIN) の OR 条件で、idx_as_approver (approver_id, status) だけでは 2段目を絞り込めない。</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>WAITING が累積すると走査が増える（年 10,000 行までは問題なし）。</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>(step_no, status) WHERE status='WAITING' の部分索引を追加。</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="63" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>AS-5</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 規格が存在しない索引 idx_as_request を参照している</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 の deleteByRequestId の備考に『idx_as_request（request_id）を利用』とあるが、schema.sql に該当索引は無い。実際は uq_approval_steps_1 (request_id, step_no) の先頭列が使われる（追加索引は不要）。</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>設計書と DDL の不一致（実害なし）。</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 規格の記載を uq_approval_steps_1 に修正する。</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="63" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>H-1</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>祝日は物理削除可で、誤削除・再計算の仕組みが無い</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>ONL-016：祝日は物理削除。削除・追加は以後の申請の日数計算にのみ影響し、作成済み requests.days は再計算しない。2000-2099 の範囲制限は ONL-016 の入力チェックのみで DB に CHECK が無い。</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>日数が祝日の追加漏れ時点の値で確定する。履歴が残らない。</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>祝日の年次一括登録手順（内閣府 CSV 取込）を運用に定義。ck_holiday_range を追加。</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
+          <t>notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48.5" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>H-2</t>
+          <t>N-3</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>祝日と会社休日を区別できない</t>
+          <t>notifications.type の値と request_id の整合を DB が保証しない</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>KF-DD-003 は「祝日・会社休日」だが種別列が無く name で区別する。</t>
+          <t>type は VARCHAR(30) NULL 可で CHECK が無く、値の妥当性と『REQUEST_* は request_id 必須・LEAVE_* は NULL』は NotificationService#notify の検証のみ。</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>会社休日のみ・祝日のみの抽出ができない。</t>
+          <t>手動 SQL・バッチで未知の type や request_id 欠落の通知が入る。</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>kind 列（NATIONAL / COMPANY）追加を検討。</t>
+          <t>ck_notif_type / ck_notif_request を追加（type が NULL の旧データは許容）。旧データを整理できれば type を NOT NULL 化。</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="77.5" customHeight="1">
+          <t>notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="92" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>N-2</t>
+          <t>N-4</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>通知の保持・削除方針が無く、取得索引も最適でない</t>
+          <t>BAT-002 規格の通知種別・重複判定が ONL-005 / 019 と不一致（要同期）</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>年 20,000 件増加。ONL-019 は最新 50 件のみ取得し、画面は先頭 5 件。idx_notif_user (user_id, is_read) の is_read を使う SELECT が無く、一覧の ORDER BY created_at DESC, id DESC のソートが残る。月次の重複確認（user_id, type, created_at 範囲）も user_id のみで絞る。</t>
+          <t>BAT-002 規格は type="MANDATORY_LEAVE_ALERT"・requestId=null が保存されない前提・message LIKE による重複確認（existsMonthlyByPattern）のままだが、ONL-005 / 019 は NotificationType.LEAVE_ALERT と existsMonthly（user_id, type, 月）を定義。BAT-001 の SQL も type を含まない INSERT のまま。</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>数年で行数が増え続ける。1 ユーザーの全通知をソートして上位 50 件を取る無駄が出る。</t>
+          <t>BAT 実装が type を設定しないと type=NULL の通知が作られ、月次重複確認（type 条件）が効かない。</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>保持 1 年を超える既読通知の削除バッチを追加。索引を (user_id, created_at DESC, id DESC) へ変更。</t>
+          <t>BAT-001 は LEAVE_GRANTED、BAT-002 は LEAVE_ALERT で notify し、重複確認は existsMonthly に統一するよう BAT 規格を更新する（担当者が更新中）。</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -2819,154 +2963,154 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="48.5" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>N-3</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>notifications.type の値と request_id の整合を DB が保証しない</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>type は VARCHAR(30) NULL 可で CHECK が無く、値の妥当性と『REQUEST_* は request_id 必須・LEAVE_* は NULL』は NotificationService#notify の検証のみ。</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>手動 SQL・バッチで未知の type や request_id 欠落の通知が入る。</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>ck_notif_type / ck_notif_request を追加（type が NULL の旧データは許容）。旧データを整理できれば type を NOT NULL 化。</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="92" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>N-4</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>BAT-002 規格の通知種別・重複判定が ONL-005 / 019 と不一致（要同期）</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>BAT-002 規格は type="MANDATORY_LEAVE_ALERT"・requestId=null が保存されない前提・message LIKE による重複確認（existsMonthlyByPattern）のままだが、ONL-005 / 019 は NotificationType.LEAVE_ALERT と existsMonthly（user_id, type, 月）を定義。BAT-001 の SQL も type を含まない INSERT のまま。</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>BAT 実装が type を設定しないと type=NULL の通知が作られ、月次重複確認（type 条件）が効かない。</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>BAT-001 は LEAVE_GRANTED、BAT-002 は LEAVE_ALERT で notify し、重複確認は existsMonthly に統一するよう BAT 規格を更新する（担当者が更新中）。</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>解消済み（v2.0）の課題：履歴</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="10" t="n"/>
-    </row>
-    <row r="40" ht="19.5" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>対象テーブル</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="92" customHeight="1">
+    <row r="39" ht="92" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>updated_at が更新時に自動更新されない</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql（set_updated_at ＋ trg_*_updated_at）／各 ONL 規格の mapping・SQL</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="77.5" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>C-2</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>application.properties（ONL-002 / ONL-019 の config）</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="106.5" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>C-1</t>
+          <t>C-3</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>updated_at が更新時に自動更新されない</t>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>schema.sql（set_updated_at ＋ trg_*_updated_at）／各 ONL 規格の mapping・SQL</t>
+          <t>V1__init_schema.sql／reset-dev.sql／application.properties（spring.flyway.*）／KF-DD-006</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2980,30 +3124,30 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="77.5" customHeight="1">
+    <row r="42" ht="106.5" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>C-2</t>
+          <t>U-1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+          <t>メールアドレスの大文字小文字の扱いが処理間で不一致</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
+          <t>保存・検索とも trim＋toLowerCase(Locale.ROOT) で正規化（ONL-001 は AuthService#login 内で実施済み。EmailNormalizer クラスは未実装で、ONL-014 実装時に共通化）。ONL-001 は正規化後の完全一致、ONL-014 の重複確認も UPPER() 比較をやめて正規化後の完全一致（uq_users_1 の索引が効く）。既存データは UPDATE users SET email = LOWER(TRIM(email)); で一度だけ移行（運用章）。</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>application.properties（ONL-002 / ONL-019 の config）</t>
+          <t>ONL-001 / ONL-014 規格</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+          <t>DB が小文字を強制していない（課題 U-4）。</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -3013,34 +3157,34 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="92" customHeight="1">
+          <t>users</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="77.5" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>U-1</t>
+          <t>U-3</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>メールアドレスの大文字小文字の扱いが処理間で不一致</t>
+          <t>ログイン失敗回数・パスワード変更日などの列が無い</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>保存・検索とも EmailNormalizer#normalize（trim＋toLowerCase(Locale.ROOT)）で正規化。ONL-001 は正規化後の完全一致、ONL-014 の重複確認も UPPER() 比較をやめて正規化後の完全一致（uq_users_1 の索引が効く）。既存データは UPDATE users SET email = LOWER(TRIM(email)); で一度だけ移行（運用章）。</t>
+          <t>users に failed_login_count（INT 既定 0）・locked_until（TIMESTAMP）・must_change_password（BOOLEAN 既定 FALSE）・password_changed_at（TIMESTAMP）を追加（V1）。ONL-001 が 5 回失敗で 30 分ロック（E-017）、ONL-023 がパスワード変更で must_change_password を false にする。</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>ONL-001 / ONL-014 規格</t>
+          <t>V1__init_schema.sql／ONL-001 / ONL-023 規格</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>DB が小文字を強制していない（課題 U-4）。</t>
+          <t>token_version（トークン失効）は未追加。無効化・ロール変更は発行済み JWT（最大 2 時間）に即時反映されない。管理者によるロック手動解除・サーバー側での mustChangePassword 強制は未実装。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -3072,7 +3216,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>schema.sql（uq_leave_balances_1）／ONL-017</t>
+          <t>V1__init_schema.sql（uq_leave_balances_1）／ONL-017</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -3146,7 +3290,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>schema.sql</t>
+          <t>V1__init_schema.sql</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -3220,7 +3364,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>schema.sql／ONL-005 / 008 / 010〜012 / 017 / 019 / 022 規格</t>
+          <t>V1__init_schema.sql／ONL-005 / 008 / 010〜012 / 017 / 019 / 022 規格</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -3242,7 +3386,7 @@
     <row r="49" ht="19.5" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>上の表は未解決の課題（34 件）。解消済みは 8 件（上の表）。ID は欠番のまま履歴として残す。</t>
+          <t>上の表は未解決の課題（32 件）。解消済みは 10 件（上の表）。ID は欠番のまま履歴として残す。</t>
         </is>
       </c>
       <c r="B49" s="9" t="n"/>
@@ -3255,8 +3399,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3270,7 +3414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3601,7 +3745,7 @@
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="6" t="inlineStr"/>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
@@ -3612,12 +3756,12 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>failed_login_count</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -3627,7 +3771,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr"/>
@@ -3644,7 +3788,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>locked_until</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -3654,34 +3798,30 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>departments</t>
+          <t>users</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>must_change_password</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -3691,38 +3831,34 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr"/>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>departments</t>
+          <t>users</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>password_changed_at</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr"/>
@@ -3735,7 +3871,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>departments</t>
+          <t>users</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -3767,7 +3903,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>departments</t>
+          <t>users</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -3799,7 +3935,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>leave_types</t>
+          <t>departments</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -3829,13 +3965,13 @@
       </c>
       <c r="H17" s="6" t="inlineStr"/>
     </row>
-    <row r="18" ht="34" customHeight="1">
+    <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>leave_types</t>
+          <t>departments</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -3855,11 +3991,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>uq_leave_types_1</t>
-        </is>
-      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="6" t="n">
@@ -3867,25 +3999,29 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>leave_types</t>
+          <t>departments</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>legal_basis</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr"/>
     </row>
@@ -3895,17 +4031,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>leave_types</t>
+          <t>departments</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>is_paid</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -3913,7 +4049,11 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
     </row>
@@ -3928,24 +4068,32 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>max_days_rule</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="H21" s="6" t="inlineStr"/>
     </row>
-    <row r="22" ht="19.5" customHeight="1">
+    <row r="22" ht="34" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>21</v>
       </c>
@@ -3956,12 +4104,12 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>allow_half_day</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -3971,7 +4119,11 @@
       </c>
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>uq_leave_types_1</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -3984,24 +4136,20 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>legal_basis</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr"/>
     </row>
@@ -4016,12 +4164,12 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_paid</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -4029,11 +4177,7 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr"/>
     </row>
@@ -4048,24 +4192,20 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>max_days_rule</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
       <c r="G25" s="6" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr"/>
     </row>
@@ -4075,17 +4215,17 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>leave_balances</t>
+          <t>leave_types</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>allow_half_day</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -4093,35 +4233,27 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
     </row>
-    <row r="27" ht="34" customHeight="1">
+    <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="6" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>leave_balances</t>
+          <t>leave_types</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -4129,35 +4261,31 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>FK→users</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>uq_leave_balances_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="6" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>leave_balances</t>
+          <t>leave_types</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>leave_type_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -4165,17 +4293,13 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr"/>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>FK→leave_types</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>uq_leave_balances_1</t>
-        </is>
-      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="6" t="n">
@@ -4183,17 +4307,17 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>leave_balances</t>
+          <t>leave_types</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>granted_days</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>DECIMAL(4,1)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -4201,7 +4325,11 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G29" s="6" t="inlineStr"/>
       <c r="H29" s="6" t="inlineStr"/>
     </row>
@@ -4216,12 +4344,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>used_days</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>DECIMAL(4,1)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -4231,10 +4359,14 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="34" customHeight="1">
@@ -4248,12 +4380,12 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>granted_on</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -4262,14 +4394,18 @@
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>FK→users</t>
+        </is>
+      </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
           <t>uq_leave_balances_1</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19.5" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>31</v>
       </c>
@@ -4280,12 +4416,12 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>expires_on</t>
+          <t>leave_type_id</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -4294,8 +4430,16 @@
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>FK→leave_types</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>uq_leave_balances_1</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="6" t="n">
@@ -4308,12 +4452,12 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>granted_days</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DECIMAL(4,1)</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -4321,11 +4465,7 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="F33" s="6" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr"/>
       <c r="H33" s="6" t="inlineStr"/>
     </row>
@@ -4340,12 +4480,12 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>used_days</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DECIMAL(4,1)</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -4355,29 +4495,29 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr"/>
       <c r="H34" s="6" t="inlineStr"/>
     </row>
-    <row r="35" ht="19.5" customHeight="1">
+    <row r="35" ht="34" customHeight="1">
       <c r="A35" s="6" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>attendance_records</t>
+          <t>leave_balances</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>granted_on</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -4385,35 +4525,31 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36" ht="34" customHeight="1">
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>uq_leave_balances_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
       <c r="A36" s="6" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>attendance_records</t>
+          <t>leave_balances</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>expires_on</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -4422,34 +4558,26 @@
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>FK→users</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>uq_attendance_records_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
       <c r="A37" s="6" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>attendance_records</t>
+          <t>leave_balances</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>work_date</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -4457,13 +4585,13 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>uq_attendance_records_1</t>
-        </is>
-      </c>
+      <c r="H37" s="6" t="inlineStr"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
       <c r="A38" s="6" t="n">
@@ -4471,12 +4599,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>attendance_records</t>
+          <t>leave_balances</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>clock_in</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4486,10 +4614,14 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr"/>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G38" s="6" t="inlineStr"/>
       <c r="H38" s="6" t="inlineStr"/>
     </row>
@@ -4504,24 +4636,32 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>clock_out</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr"/>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="H39" s="6" t="inlineStr"/>
     </row>
-    <row r="40" ht="19.5" customHeight="1">
+    <row r="40" ht="34" customHeight="1">
       <c r="A40" s="6" t="n">
         <v>39</v>
       </c>
@@ -4532,24 +4672,32 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>work_minutes</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="19.5" customHeight="1">
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>FK→users</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>uq_attendance_records_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
@@ -4560,22 +4708,26 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>overtime_minutes</t>
+          <t>work_date</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>uq_attendance_records_1</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="19.5" customHeight="1">
       <c r="A42" s="6" t="n">
@@ -4588,7 +4740,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>clock_in</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -4598,14 +4750,10 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr"/>
       <c r="H42" s="6" t="inlineStr"/>
     </row>
@@ -4620,7 +4768,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>clock_out</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -4630,14 +4778,10 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr"/>
       <c r="H43" s="6" t="inlineStr"/>
     </row>
@@ -4647,34 +4791,26 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>attendance_records</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>work_minutes</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
       <c r="H44" s="6" t="inlineStr"/>
     </row>
     <row r="45" ht="19.5" customHeight="1">
@@ -4683,30 +4819,26 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>attendance_records</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>overtime_minutes</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>FK→users</t>
-        </is>
-      </c>
+      <c r="G45" s="6" t="inlineStr"/>
       <c r="H45" s="6" t="inlineStr"/>
     </row>
     <row r="46" ht="19.5" customHeight="1">
@@ -4715,17 +4847,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>attendance_records</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>request_type</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -4733,40 +4865,44 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G46" s="6" t="inlineStr"/>
       <c r="H46" s="6" t="inlineStr"/>
     </row>
-    <row r="47" ht="34" customHeight="1">
+    <row r="47" ht="19.5" customHeight="1">
       <c r="A47" s="6" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>requests</t>
+          <t>attendance_records</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>leave_type_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr"/>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>FK→leave_types</t>
-        </is>
-      </c>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr"/>
       <c r="H47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
@@ -4780,12 +4916,12 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -4793,8 +4929,16 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr"/>
-      <c r="G48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="H48" s="6" t="inlineStr"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
@@ -4808,12 +4952,12 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -4822,7 +4966,11 @@
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
-      <c r="G49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>FK→users</t>
+        </is>
+      </c>
       <c r="H49" s="6" t="inlineStr"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
@@ -4836,7 +4984,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>request_type</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -4846,14 +4994,14 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
       <c r="G50" s="6" t="inlineStr"/>
       <c r="H50" s="6" t="inlineStr"/>
     </row>
-    <row r="51" ht="19.5" customHeight="1">
+    <row r="51" ht="34" customHeight="1">
       <c r="A51" s="6" t="n">
         <v>50</v>
       </c>
@@ -4864,12 +5012,12 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>leave_type_id</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>DECIMAL(4,1)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -4878,10 +5026,14 @@
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
-      <c r="G51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>FK→leave_types</t>
+        </is>
+      </c>
       <c r="H51" s="6" t="inlineStr"/>
     </row>
-    <row r="52" ht="34" customHeight="1">
+    <row r="52" ht="19.5" customHeight="1">
       <c r="A52" s="6" t="n">
         <v>51</v>
       </c>
@@ -4892,24 +5044,24 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>corrected_clock_in</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
       <c r="G52" s="6" t="inlineStr"/>
       <c r="H52" s="6" t="inlineStr"/>
     </row>
-    <row r="53" ht="34" customHeight="1">
+    <row r="53" ht="19.5" customHeight="1">
       <c r="A53" s="6" t="n">
         <v>52</v>
       </c>
@@ -4920,17 +5072,17 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>corrected_clock_out</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -4948,12 +5100,12 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -4976,24 +5128,24 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DECIMAL(4,1)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
       <c r="G55" s="6" t="inlineStr"/>
       <c r="H55" s="6" t="inlineStr"/>
     </row>
-    <row r="56" ht="19.5" customHeight="1">
+    <row r="56" ht="34" customHeight="1">
       <c r="A56" s="6" t="n">
         <v>55</v>
       </c>
@@ -5004,24 +5156,24 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>current_step</t>
+          <t>corrected_clock_in</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
       <c r="G56" s="6" t="inlineStr"/>
       <c r="H56" s="6" t="inlineStr"/>
     </row>
-    <row r="57" ht="19.5" customHeight="1">
+    <row r="57" ht="34" customHeight="1">
       <c r="A57" s="6" t="n">
         <v>56</v>
       </c>
@@ -5032,7 +5184,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>corrected_clock_out</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -5060,24 +5212,20 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr"/>
       <c r="G58" s="6" t="inlineStr"/>
       <c r="H58" s="6" t="inlineStr"/>
     </row>
@@ -5092,12 +5240,12 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -5105,11 +5253,7 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="F59" s="6" t="inlineStr"/>
       <c r="G59" s="6" t="inlineStr"/>
       <c r="H59" s="6" t="inlineStr"/>
     </row>
@@ -5119,17 +5263,17 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>approval_steps</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>current_step</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -5137,71 +5281,55 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr"/>
       <c r="H60" s="6" t="inlineStr"/>
     </row>
-    <row r="61" ht="34" customHeight="1">
+    <row r="61" ht="19.5" customHeight="1">
       <c r="A61" s="6" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>approval_steps</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>submitted_at</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>FK→requests</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>uq_approval_steps_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="34" customHeight="1">
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
       <c r="A62" s="6" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>approval_steps</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>step_no</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -5209,13 +5337,13 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>uq_approval_steps_1</t>
-        </is>
-      </c>
+      <c r="H62" s="6" t="inlineStr"/>
     </row>
     <row r="63" ht="19.5" customHeight="1">
       <c r="A63" s="6" t="n">
@@ -5223,30 +5351,30 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>approval_steps</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>approver_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr"/>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>FK→users</t>
-        </is>
-      </c>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr"/>
       <c r="H63" s="6" t="inlineStr"/>
     </row>
     <row r="64" ht="19.5" customHeight="1">
@@ -5260,12 +5388,12 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -5273,11 +5401,19 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr"/>
-      <c r="G64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="H64" s="6" t="inlineStr"/>
     </row>
-    <row r="65" ht="19.5" customHeight="1">
+    <row r="65" ht="34" customHeight="1">
       <c r="A65" s="6" t="n">
         <v>64</v>
       </c>
@@ -5288,24 +5424,32 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>request_id</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
-      <c r="G65" s="6" t="inlineStr"/>
-      <c r="H65" s="6" t="inlineStr"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>FK→requests</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>uq_approval_steps_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="34" customHeight="1">
       <c r="A66" s="6" t="n">
         <v>65</v>
       </c>
@@ -5316,22 +5460,26 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>acted_at</t>
+          <t>step_no</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
       <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>uq_approval_steps_1</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="19.5" customHeight="1">
       <c r="A67" s="6" t="n">
@@ -5344,25 +5492,25 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>approver_id</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr"/>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>FK→users</t>
+        </is>
+      </c>
       <c r="H67" s="6" t="inlineStr"/>
     </row>
     <row r="68" ht="19.5" customHeight="1">
@@ -5376,12 +5524,12 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -5389,11 +5537,7 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="F68" s="6" t="inlineStr"/>
       <c r="G68" s="6" t="inlineStr"/>
       <c r="H68" s="6" t="inlineStr"/>
     </row>
@@ -5403,34 +5547,26 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
+          <t>approval_steps</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr"/>
     </row>
     <row r="70" ht="19.5" customHeight="1">
@@ -5439,31 +5575,27 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
+          <t>approval_steps</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>holiday_date</t>
+          <t>acted_at</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
       <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>uq_holidays_1</t>
-        </is>
-      </c>
+      <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71" ht="19.5" customHeight="1">
       <c r="A71" s="6" t="n">
@@ -5471,17 +5603,17 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
+          <t>approval_steps</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -5489,7 +5621,11 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G71" s="6" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr"/>
     </row>
@@ -5499,12 +5635,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
+          <t>approval_steps</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -5536,12 +5672,12 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -5551,10 +5687,14 @@
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="H73" s="6" t="inlineStr"/>
     </row>
     <row r="74" ht="19.5" customHeight="1">
@@ -5563,17 +5703,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>holidays</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>holiday_date</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -5581,17 +5721,13 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="inlineStr"/>
+      <c r="F74" s="6" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>uq_holidays_1</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="19.5" customHeight="1">
       <c r="A75" s="6" t="n">
@@ -5599,17 +5735,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>holidays</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -5618,11 +5754,7 @@
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>FK→users</t>
-        </is>
-      </c>
+      <c r="G75" s="6" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr"/>
     </row>
     <row r="76" ht="19.5" customHeight="1">
@@ -5631,58 +5763,62 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>holidays</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr"/>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G76" s="6" t="inlineStr"/>
       <c r="H76" s="6" t="inlineStr"/>
     </row>
-    <row r="77" ht="34" customHeight="1">
+    <row r="77" ht="19.5" customHeight="1">
       <c r="A77" s="6" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>holidays</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr"/>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>FK→requests</t>
-        </is>
-      </c>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr"/>
       <c r="H77" s="6" t="inlineStr"/>
     </row>
     <row r="78" ht="19.5" customHeight="1">
@@ -5696,12 +5832,12 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -5709,8 +5845,16 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr"/>
-      <c r="G78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="H78" s="6" t="inlineStr"/>
     </row>
     <row r="79" ht="19.5" customHeight="1">
@@ -5724,12 +5868,12 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>is_read</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -5737,12 +5881,12 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>FK→users</t>
+        </is>
+      </c>
       <c r="H79" s="6" t="inlineStr"/>
     </row>
     <row r="80" ht="19.5" customHeight="1">
@@ -5756,28 +5900,24 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr"/>
       <c r="G80" s="6" t="inlineStr"/>
       <c r="H80" s="6" t="inlineStr"/>
     </row>
-    <row r="81" ht="19.5" customHeight="1">
+    <row r="81" ht="34" customHeight="1">
       <c r="A81" s="6" t="n">
         <v>80</v>
       </c>
@@ -5788,44 +5928,168 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
+          <t>request_id</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>FK→requests</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>is_read</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr"/>
-    </row>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>schema.sql の自動生成。個別の説明は各テーブル詳細設計書の 2章を参照。</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="n"/>
-      <c r="C82" s="9" t="n"/>
-      <c r="D82" s="9" t="n"/>
-      <c r="E82" s="9" t="n"/>
-      <c r="F82" s="9" t="n"/>
-      <c r="G82" s="9" t="n"/>
-      <c r="H82" s="10" t="n"/>
+      <c r="G85" s="6" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql の自動生成。個別の説明は各テーブル詳細設計書の 2章を参照。</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="A86:H86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5839,7 +6103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5921,6 +6185,29 @@
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>DB のスキーマ管理を Flyway に変更（backend/schema.sql の手動実行を廃止し、db/migration/V1__init_schema.sql を Flyway が適用。V1 は編集しない。開発 DB の作り直しは backend/db/reset-dev.sql）。users に 4 列（failed_login_count / locked_until / must_change_password / password_changed_at）を追加（ONL-001 のアカウントロック、ONL-023 のパスワード変更）。初期データの部署を 3 件から 5 件に、開発用ユーザーを 4 件から 100 件に更新。CRUD マトリクスに ONL-023 を追加。課題 C-3・U-3 を解消済みへ。</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5962,7 +6249,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>PostgreSQL 18（開発・本番とも）。H2 は使用しない。なお本書の SQL・INSERT 例・確認用 SQL は PostgreSQL 16 上で schema.sql に対して実行確認した（PostgreSQL 18 固有機能は使用していない）。</t>
+          <t>PostgreSQL 18（開発・本番とも）。H2 は使用しない。なお本書の SQL・INSERT 例・確認用 SQL は PostgreSQL 16 上で V1__init_schema.sql に対して実行確認した（PostgreSQL 18 固有機能は使用していない）。</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6321,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>共通関数 set_updated_at()（PL/pgSQL。NEW.updated_at = CURRENT_TIMESTAMP を返す）を、全 9 表の BEFORE UPDATE FOR EACH ROW トリガ trg_&lt;表&gt;_updated_at から呼ぶ（schema.sql 末尾）。CURRENT_TIMESTAMP はトランザクション開始時刻のため同一トランザクション内の更新は同じ値になる。値が変わらない UPDATE や updated_at を明示した UPDATE でも上書きする。INSERT では動かない。pg_dump / 復元（COPY）ではトリガは発火しない。</t>
+          <t>共通関数 set_updated_at()（PL/pgSQL。NEW.updated_at = CURRENT_TIMESTAMP を返す）を、全 9 表の BEFORE UPDATE FOR EACH ROW トリガ trg_&lt;表&gt;_updated_at から呼ぶ（V1__init_schema.sql 末尾）。CURRENT_TIMESTAMP はトランザクション開始時刻のため同一トランザクション内の更新は同じ値になる。値が変わらない UPDATE や updated_at を明示した UPDATE でも上書きする。INSERT では動かない。pg_dump / 復元（COPY）ではトリガは発火しない。</t>
         </is>
       </c>
     </row>
@@ -6058,11 +6345,11 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>backend/schema.sql を手動実行し、アプリは spring.jpa.hibernate.ddl-auto=validate で Entity との整合を起動時に検証する（詳細は『マイグレーション方針』）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
+          <t>Flyway（backend/src/main/resources/db/migration/V&lt;連番&gt;__&lt;内容&gt;.sql）がアプリ起動時にスキーマを作成・更新する。アプリは spring.jpa.hibernate.ddl-auto=validate で Entity との整合を起動時に検証する（詳細は『マイグレーション方針』）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>DDL</t>
@@ -6070,7 +6357,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>backend/schema.sql（本書および KF-DD-TBL-01〜09 の列・制約・索引は同ファイルから自動生成）</t>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql（本書および KF-DD-TBL-01〜09 の列・制約・索引は同ファイルから自動生成）</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:L38"/>
+  <dimension ref="A2:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6748,7 +7035,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R/U</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
@@ -6810,7 +7097,7 @@
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
@@ -6840,7 +7127,7 @@
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6866,18 +7153,18 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6893,7 +7180,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6922,14 +7209,14 @@
       </c>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr"/>
       <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -6954,33 +7241,33 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7004,7 +7291,7 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7013,12 +7300,12 @@
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr"/>
       <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7046,12 +7333,12 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7059,12 +7346,12 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7088,18 +7375,18 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>R*</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
@@ -7109,12 +7396,12 @@
           <t>C/R/U</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
@@ -7142,7 +7429,7 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7151,12 +7438,12 @@
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
@@ -7184,7 +7471,7 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7193,12 +7480,12 @@
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
@@ -7226,24 +7513,24 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7273,7 +7560,7 @@
           <t>C/R/U</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7362,13 +7649,13 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7404,24 +7691,24 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7454,7 +7741,7 @@
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr"/>
       <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="14" t="inlineStr">
+      <c r="L22" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
@@ -7476,24 +7763,24 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7520,7 +7807,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7548,24 +7835,24 @@
           <t>ONL</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
@@ -7575,7 +7862,7 @@
           <t>C/D</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="K25" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
@@ -7589,54 +7876,42 @@
     <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-023</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>年次有給休暇 自動付与</t>
+          <t>パスワード変更</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>ONL</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R/U</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>C/R</t>
-        </is>
-      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="6" t="inlineStr"/>
       <c r="K26" s="6" t="inlineStr"/>
-      <c r="L26" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>BAT-002</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>年5日取得義務アラート</t>
+          <t>年次有給休暇 自動付与</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -7644,396 +7919,438 @@
           <t>BAT</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>C/R</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I27" s="6" t="inlineStr"/>
       <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr"/>
       <c r="L27" s="13" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>年5日取得義務アラート</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
           <t>C/R</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>BAT</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H28" s="12" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J28" s="12" t="inlineStr">
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K28" s="12" t="inlineStr">
+      <c r="K29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L29" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
-      </c>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="16" t="inlineStr"/>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>集計：C 登録する処理数</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr"/>
-      <c r="D29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="16" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="16" t="inlineStr"/>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>集計：R 参照する処理数</t>
+          <t>集計：C 登録する処理数</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr"/>
       <c r="D30" s="16" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G30" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="16" t="n">
         <v>9</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="J30" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="K30" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L30" s="16" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="16" t="inlineStr"/>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>集計：U 更新する処理数</t>
+          <t>集計：R 参照する処理数</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr"/>
       <c r="D31" s="16" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G31" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J31" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K31" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" s="16" t="n">
         <v>3</v>
-      </c>
-      <c r="H31" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="16" t="inlineStr"/>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>集計：D 削除する処理数</t>
+          <t>集計：U 更新する処理数</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr"/>
       <c r="D32" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="16" t="n">
+      <c r="L32" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="16" t="inlineStr"/>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>集計：D 削除する処理数</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr"/>
+      <c r="D33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="16" t="n">
+      <c r="E33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="16" t="n">
+      <c r="F33" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="16" t="n">
+      <c r="G33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="16" t="n">
+      <c r="K33" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="L32" s="16" t="n">
+      <c r="L33" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>凡例：C=登録（INSERT）／R=参照（SELECT。FOR UPDATE による行ロックを含む）／U=更新（UPDATE）／D=削除（DELETE）。色は D＞C＞U＞R の優先で表示。* の付いた操作は、規格の『使用テーブル（tables）』欄に記載が無く、規格の SQL 欄にのみ現れるもの（下の突合結果を参照）。BAT-003 は pg_dump による全テーブルの読取（R）。</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
-      <c r="L33" s="10" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>CRUD 突合結果（規格 tables と SQL 欄の差異。矛盾ではなく tables 欄の記載漏れ）</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="10" t="n"/>
-    </row>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>テーブル</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>規格 tables の記載</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>SQL 欄から読み取れる操作</t>
-        </is>
-      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
       <c r="G36" s="9" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>判断</t>
-        </is>
-      </c>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="9" t="n"/>
       <c r="L36" s="10" t="n"/>
     </row>
     <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>leave_types</t>
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>テーブル</t>
         </is>
       </c>
       <c r="C37" s="10" t="n"/>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>記載なし</t>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>規格 tables の記載</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>SQL 欄から読み取れる操作</t>
         </is>
       </c>
       <c r="G37" s="9" t="n"/>
       <c r="H37" s="10" t="n"/>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>consume 内で種別を読む（参考記載）。R を追記推奨</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>判断</t>
         </is>
       </c>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="9" t="n"/>
       <c r="L37" s="10" t="n"/>
     </row>
-    <row r="38" ht="34" customHeight="1">
+    <row r="38" ht="19.5" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>leave_types</t>
         </is>
       </c>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>記載なし</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>SQL 欄に INSERT なし（mapping と methods に notify 呼出しあり）</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G38" s="9" t="n"/>
       <c r="H38" s="10" t="n"/>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>tables 欄が正。SQL 欄に NotificationService#notify の INSERT を追記推奨</t>
+          <t>consume 内で種別を読む（参考記載）。R を追記推奨</t>
         </is>
       </c>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="9" t="n"/>
       <c r="L38" s="10" t="n"/>
     </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ONL-017</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>SQL 欄に INSERT なし（mapping と methods に notify 呼出しあり）</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>tables 欄が正。SQL 欄に NotificationService#notify の INSERT を追記推奨</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
+      <c r="L39" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F38:H38"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="F39:H39"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="D37:E37"/>
+    <mergeCell ref="A36:L36"/>
     <mergeCell ref="D38:E38"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="I38:L38"/>
-    <mergeCell ref="D36:E36"/>
     <mergeCell ref="F37:H37"/>
-    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A34:L34"/>
     <mergeCell ref="I37:L37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8070,7 +8387,7 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>例（schema.sql）</t>
+          <t>例（V1__init_schema.sql）</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
@@ -8190,7 +8507,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>（schema.sql では無名＝ &lt;表&gt;_pkey が自動付与）</t>
+          <t>（V1__init_schema.sql では無名＝ &lt;表&gt;_pkey が自動付与）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">

--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-003_テーブル設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-003_テーブル設計書.xlsx
@@ -17,9 +17,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="型方針" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="削除方針" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初期データ" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マイグレーション方針" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横断課題一覧" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全列一覧" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初期データ・開発用シード" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マイグレーション方針" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横断課題一覧" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全列一覧" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -302,7 +303,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="15240000" cy="11306175"/>
+    <ext cx="15240000" cy="13858875"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -316,6 +317,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -613,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B3:C13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -621,6 +625,8 @@
     <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="1" t="inlineStr">
         <is>
@@ -631,10 +637,12 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>総覧：ER 図・CRUD マトリクス・規約（個別は KF-DD-TBL-01〜09）</t>
-        </is>
-      </c>
-    </row>
+          <t>総覧：ER 図・CRUD マトリクス・規約（個別は KF-DD-TBL-01〜10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -679,7 +687,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
     </row>
@@ -715,7 +723,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>KF-DD-TBL-01〜09（テーブル詳細設計書）／ backend/src/main/resources/db/migration/V1__init_schema.sql</t>
+          <t>KF-DD-TBL-01〜10（テーブル詳細設計書）／ backend/src/main/resources/db/migration の V1__init_schema.sql・V2__seed_holidays.sql・V3__seed_holidays_2028.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql</t>
         </is>
       </c>
     </row>
@@ -731,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G36"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -743,6 +751,7 @@
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
@@ -1151,6 +1160,7 @@
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="10" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
@@ -1256,10 +1266,11 @@
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>開発用ユーザー users（100 件。V1 ではなく DevDataInitializer が userRepository.count() = 0 かつ seed-password 設定時のみ作成。本番では使用しない）</t>
+          <t>祝日・会社休日 holidays（64 件。V2__seed_holidays.sql＝2026〜2027 年 43 件、V3__seed_holidays_2028.sql＝2028 年 21 件。年別：2026 年 21 件・2027 年 22 件・2028 年 21 件）</t>
         </is>
       </c>
       <c r="B25" s="9" t="n"/>
@@ -1277,57 +1288,49 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>メール</t>
+          <t>日付</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>氏名 / ロール</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>部署</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>上長</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="63" customHeight="1">
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>投入元</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>admin@example.com 、adm002@example.com</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>人事 管理者 ほか / ADMIN（2 名）</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>管理部</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>全員 hire_date=2024-04-01 相当、status=ACTIVE、must_change_password=FALSE、パスワードは設定値を BCrypt 化（$2a$10$...）</t>
-        </is>
-      </c>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="6" t="n">
@@ -1335,25 +1338,21 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>adm003@example.com</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>（架空氏名）/ MANAGER</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>管理部</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
@@ -1362,205 +1361,1554 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>adm004〜adm010@example.com</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>（架空氏名）/ EMPLOYEE（7 名）</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>管理部</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>adm003</t>
-        </is>
-      </c>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr"/>
       <c r="G29" s="6" t="inlineStr"/>
     </row>
-    <row r="30" ht="34" customHeight="1">
+    <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>manager@example.com 、dev002@example.com</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>佐藤 一郎 ほか / MANAGER（2 名）</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>システム開発事業部</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>なし</t>
-        </is>
-      </c>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr"/>
     </row>
-    <row r="31" ht="63" customHeight="1">
+    <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>taro@example.com 、hanako@example.com 、dev005〜dev030@example.com</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>山田 太郎、鈴木 花子 ほか / EMPLOYEE（28 名）</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>システム開発事業部</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>manager@ / dev002@（番号の偶奇で振分け）</t>
-        </is>
-      </c>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr"/>
     </row>
-    <row r="32" ht="34" customHeight="1">
+    <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>sol001〜sol025@example.com</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 23</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>ソリューション事業部</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>sol001 / sol002</t>
-        </is>
-      </c>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr"/>
     </row>
-    <row r="33" ht="34" customHeight="1">
+    <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>sap001〜sap020@example.com</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 18</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>SAP事業部</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>sap001 / sap002</t>
-        </is>
-      </c>
+          <t>憲法記念日</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr"/>
     </row>
-    <row r="34" ht="34" customHeight="1">
+    <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>cld001〜cld015@example.com</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 13</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>クラウド基盤サービス部</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>cld001 / cld002</t>
-        </is>
-      </c>
+          <t>みどりの日</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
       <c r="G34" s="6" t="inlineStr"/>
     </row>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>本番の初期管理者は BootstrapAdminInitializer が users が空かつ設定が揃うときだけ 1 名作成する（部署=管理部、must_change_password=TRUE）。</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="10" t="n"/>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>その他の表（leave_balances / attendance_records / requests / approval_steps / holidays / notifications）の初期データは無い。祝日は管理者が ONL-016 で登録する。</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="10" t="n"/>
+      <c r="A35" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>休日（憲法記念日の振替休日）</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="A38" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="A39" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="A40" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>国民の休日</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="A43" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="A45" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-30</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-02</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-03</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-11</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>2027-02-11</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>2027-02-23</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="A54" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>2027-03-21</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="A55" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>2027-03-22</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>休日（春分の日の振替休日）</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="A56" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>2027-04-29</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="A57" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>2027-05-03</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>憲法記念日</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="A58" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>2027-05-04</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>みどりの日</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="A59" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>2027-05-05</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="A60" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>2027-07-19</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>2027-08-11</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="A62" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>2027-09-20</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="A63" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>2027-09-23</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64" ht="19.5" customHeight="1">
+      <c r="A64" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>2027-10-11</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="A65" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>2027-11-03</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="A66" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>2027-11-23</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67" ht="19.5" customHeight="1">
+      <c r="A67" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>2027-12-29</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="A68" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>2027-12-30</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="6" t="inlineStr"/>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="A69" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>2027-12-31</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="6" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="A70" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>2028-01-01</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>元日</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="A71" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>2028-01-02</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="A72" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>2028-01-03</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="6" t="inlineStr"/>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="19.5" customHeight="1">
+      <c r="A73" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>2028-01-10</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>成人の日</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="A74" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>2028-02-11</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>建国記念の日</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="6" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="A75" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>2028-02-23</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>天皇誕生日</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="6" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76" ht="19.5" customHeight="1">
+      <c r="A76" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>2028-03-20</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>春分の日</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="6" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="A77" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>2028-04-29</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>昭和の日</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="6" t="inlineStr"/>
+      <c r="G77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>2028-05-03</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>憲法記念日</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79" ht="19.5" customHeight="1">
+      <c r="A79" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>2028-05-04</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>みどりの日</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="A80" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>2028-05-05</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>こどもの日</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1">
+      <c r="A81" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>2028-07-17</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>海の日</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="6" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>2028-08-11</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>山の日</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="A83" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>2028-09-18</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>敬老の日</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr"/>
+      <c r="F83" s="6" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84" ht="19.5" customHeight="1">
+      <c r="A84" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>2028-09-22</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>秋分の日</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85" ht="19.5" customHeight="1">
+      <c r="A85" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>2028-10-09</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>スポーツの日</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="6" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="A86" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>2028-11-03</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>文化の日</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>2028-11-23</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>勤労感謝の日</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
+      <c r="A88" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>2028-12-29</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr"/>
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>2028-12-30</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="A90" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>2028-12-31</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>年末年始休暇（会社休日）</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>会社休日（年末年始）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="48.5" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>出典：内閣府が公表する国民の祝日（振替休日・国民の休日を含む）。年末年始（12/29〜1/3）は会社休日として同じ表に登録（KF-RD-002）。範囲は 2026-01-01〜2028-12-31 で、2026-01-02・01-03 と 2029 年以降は含まない。V3（2028 年）は祝日法の規則に基づく推算値で、内閣府の公表値との照合は未実施（課題 H-4）。2028 年は祝日が日曜に重ならないため振替休日はない。</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="n"/>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="10" t="n"/>
+    </row>
+    <row r="92" ht="48.5" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>冪等性：V2・V3 とも INSERT は ON CONFLICT (holiday_date) DO NOTHING。同じ日付が既にあれば何もせず（ONL-016 で登録済みの行も名称を変えない）、再実行しても件数は増えない。IDENTITY の採番値は飛ばした行でも進むため id に欠番が出ることがある。Flyway は各版を 1 回だけ実行し、適用後は編集しない。</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="10" t="n"/>
+    </row>
+    <row r="93" ht="48.5" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>毎年の追加（運用）：2029 年以降は ONL-016（祝日管理）で登録する。目安は毎年 2 月頃に翌年分。2029 年 1 月の元日と年始の会社休日（1/2・1/3）は 2028 年内に登録する（V3 は 2028 年 1 月分と 12/29〜31 までで、2029 年 1 月は含まない）。新規環境にも同じ祝日を入れる場合は V6 以降のマイグレーションに ON CONFLICT DO NOTHING の INSERT を追加する（課題 H-3）。</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="10" t="n"/>
+    </row>
+    <row r="94" ht="34" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>V4（attendance_breaks の追加）と V5（requests への休憩・離席修正の 3 列と制約の追加）は DDL のみで、初期データを持たない（V5 で追加した 3 列は既存の requests 行では NULL のまま）。</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="10" t="n"/>
+    </row>
+    <row r="95" ht="34" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>その他の表（users / leave_balances / attendance_records / attendance_breaks / requests / approval_steps / notifications）は Flyway の初期データを持たない。開発用ユーザー・初期管理者・開発用の年休付与は『初期データ・開発用シード』シートを参照。</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="C29:D29"/>
+  <mergeCells count="9">
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A94:G94"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A91:G91"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A95:G95"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1574,137 +2922,971 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="120" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>1. 初期データの分類（何が・どの処理で・どの条件で入るか）</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="10" t="n"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="63" customHeight="1">
-      <c r="A2" s="6" t="n">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>投入元</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>対象表</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>実行条件</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>投入内容</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>使う環境</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>現状</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Flyway で管理する。backend/src/main/resources/db/migration/V1__init_schema.sql（DDL・トリガ・初期データ。DROP は含まない）をアプリ起動時に自動適用する。旧 backend/schema.sql（手動実行・先頭に DROP）は廃止（解消済み C-3）。Spring Boot 側は spring.jpa.hibernate.ddl-auto=validate とし、起動時に Entity と DB の型・列の整合を検証する（DDL を自動生成・変更させない）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="63" customHeight="1">
-      <c r="A3" s="6" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>マスタ初期データ（V1）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Flyway：V1__init_schema.sql</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>departments / leave_types</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Flyway が 1 回だけ適用（空の DB の初回起動）</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>部署 5 件・休暇種別 11 件</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>全環境（本番を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>適用手順（現行）</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>①空の DB を作成（運用接続用に ALTER DATABASE ... SET timezone TO 'Asia/Tokyo' を併用。課題 C-6）②アプリ（または docker compose up -d --build）を起動すると Flyway が V1 を適用（テーブル・索引・関数 set_updated_at・トリガ・初期データ）③Hikari の connection-init-sql で JST に固定され、ddl-auto=validate が通ることを確認④開発のみ DevDataInitializer が開発用ユーザーを、本番は BootstrapAdminInitializer が初期管理者を作る。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="48.5" customHeight="1">
-      <c r="A4" s="6" t="n">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>祝日初期データ（V2・V3）</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Flyway：V2__seed_holidays.sql・V3__seed_holidays_2028.sql</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>同上。ON CONFLICT (holiday_date) DO NOTHING（冪等）</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>V2：2026〜2027 年 43 件、V3：2028 年 21 件（計 64 件。V3 の日付は推算値で公表値と未照合）</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>全環境（本番を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="63" customHeight="1">
+      <c r="A6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>変更の入れ方</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>V1 は適用後に編集しない（Flyway がチェックサムを検証し、編集すると起動に失敗する）。列・制約・索引の変更は V2__&lt;内容&gt;.sql のように新しいファイルを追加する。本番適用前に件数・重複の確認 SQL（各テーブル詳細設計書 10章）で既存データが新制約を満たすことを確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48.5" customHeight="1">
-      <c r="A5" s="6" t="n">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>開発用ユーザー</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>DevDataInitializer（@Order 1）</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>kintaiflow.dev.seed-enabled=true（@ConditionalOnProperty）かつ kintaiflow.dev.seed-password が空でない かつ users が 0 件</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>架空ユーザー 100 名（管理部 10＋技術者 90）。全員同じ初期パスワード</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>開発（local）専用。application-local.properties に seed-enabled=true を設定。本番では未設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>既存の開発 DB</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>旧 schema.sql で作った DB は spring.flyway.baseline-on-migrate=true・baseline-version=1 により V1 適用済みとして取り込まれる。ただし V1 に含まれる新しい列（users の 4 列）は追加されず、ddl-auto=validate で起動に失敗する。backend/db/reset-dev.sql（DROP SCHEMA public CASCADE; CREATE SCHEMA public;）で作り直す。本番では実行しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48.5" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>初期管理者</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer（@Order 2）</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>KINTAIFLOW_BOOTSTRAP_ADMIN_EMAIL・_PASSWORD が両方あり かつ users が 0 件</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>管理者 1 名（初回ログインでパスワード変更必須）</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>本番の初回起動</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48.5" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>既存データの移行（email 小文字化）</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>既存 DB に大文字混じりのメールがある場合のみ。①重複確認 SELECT LOWER(BTRIM(email)), COUNT(*) FROM users GROUP BY 1 HAVING COUNT(*) &gt; 1;（0 行）②UPDATE users SET email = LOWER(TRIM(email));（ONL-014 導入時の注意。トリガにより updated_at も更新される）。詳細は KF-DD-TBL-01 の運用章。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="63" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>開発用の年休付与</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>DevLeaveBalanceInitializer（@Order 3）</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>seed-enabled=true かつ seed-password が空でない かつ leave_balances が 0 件 かつ users が 1 件以上</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>ACTIVE の全ユーザーへ年次有給休暇 20 日（当年度 4/1 付与）</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>開発（local）専用</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="63" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>保留中の変更案</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>各詳細設計書 3.4 の推奨 DDL（採否は課題一覧の優先度で決める）：idx_lb_user 廃止（LB-6）、ck_users_email_lower（U-4）、requests / leave_balances / attendance_records の CHECK、notifications の ck_notif_type・ck_notif_request（N-3）と索引置換（N-2）。解消済みの項目（updated_at トリガ・notifications の type/request_id・uq_leave_balances_1・idx_att_user_date 削除）は V1__init_schema.sql に反映済み。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="6" t="n">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>DDL のみのマイグレーション（V4・V5）</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Flyway：V4__attendance_breaks.sql・V5__break_correction_request.sql</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks（新規）／ requests（列・制約の追加）</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Flyway が 1 回だけ適用</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>初期データなし。V4 は表・索引・トリガの作成、V5 は requests に 3 列（NULL 可）と制約 ck_req_type（再作成）・ck_req_break_kind を追加</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>全環境（本番を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48.5" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>1・2・6 は SQL（Flyway）、3〜5 はアプリ起動時に動く CommandLineRunner（Java）。3〜5 は Flyway の履歴には残らず、条件を満たす間は起動のたびに判定するが、対象表にデータがあれば何もしない（二重に作らない）。実行順は Flyway → DevDataInitializer → BootstrapAdminInitializer → DevLeaveBalanceInitializer。BootstrapAdminInitializer（4）は seed-enabled に関係なく従来どおり動く（環境変数が両方あり users が 0 件のとき）。</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="63" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>『local 環境』は Spring のプロファイルではない。いずれも @Profile を持たず、プロパティ kintaiflow.dev.seed-enabled=true（@ConditionalOnProperty。DevDataInitializer・DevLeaveBalanceInitializer が対象）と seed-password の有無で動く。seed-enabled は application-local.properties（Git 管理外。application.properties が optional で読み込む。この環境では true を設定済み）に置き、本番では設定しない。seed-password の値は application-local.properties または環境変数 KINTAIFLOW_DEV_SEED_PASSWORD（Docker Compose では .env の DEV_SEED_PASSWORD）で与える（課題 U-5）。なお docker-compose.yml が backend に渡す開発用の環境変数は KINTAIFLOW_DEV_SEED_PASSWORD のみで、seed-enabled（環境変数なら KINTAIFLOW_DEV_SEED_ENABLED）は渡していないため、Compose 起動では開発用シードは動かない（動かす場合は compose に追加する。要確認）。</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="10" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>2. 開発用ユーザー users（100 名。DevDataInitializer）</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>氏名 / ロール</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>部署</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>上長</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>admin@example.com 、adm002@example.com</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>人事 管理者 ほか / ADMIN（2 名）</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>管理部</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>代表アカウント：admin@（管理者）</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>adm003@example.com</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ MANAGER（1 名）</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>管理部</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>管理部の上長</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>adm004〜adm010@example.com</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ EMPLOYEE（7 名）</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>管理部</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>adm003</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>manager@example.com 、dev002@example.com</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>佐藤 一郎 ほか / MANAGER（2 名）</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>システム開発事業部</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>代表アカウント：manager@（上長）</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48.5" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>taro@example.com 、hanako@example.com 、dev005〜dev030@example.com</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>山田 太郎、鈴木 花子 ほか / EMPLOYEE（28 名）</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>システム開発事業部</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>manager@ / dev002@</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>代表アカウント：taro@・hanako@（社員。上長は manager@）。dev005〜は番号が偶数なら manager@、奇数なら dev002@</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>sol001〜sol025@example.com</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 23</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>ソリューション事業部</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>sol001 / sol002</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>003 以降は番号の偶奇で振分け（偶数＝001）</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>バックアップ・復元</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>BAT-003 が毎日 pg_dump（プレーン SQL）で 7 世代保存。復元は psql -f。復元後は IDENTITY のシーケンスが最大 id を超えていることを確認する。</t>
-        </is>
-      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>sap001〜sap020@example.com</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 18</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>SAP事業部</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>sap001 / sap002</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>cld001〜cld015@example.com</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>（架空氏名）/ MANAGER 2 + EMPLOYEE 13</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>クラウド基盤サービス部</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>cld001 / cld002</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>100 名＝ADMIN 2・MANAGER 9・EMPLOYEE 89（管理部 10＋システム開発 30＋ソリューション 25＋SAP 20＋クラウド基盤 15）。メールはすべて @example.com。</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>共通の値</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>status=ACTIVE、must_change_password=FALSE、failed_login_count=0、locked_until・password_changed_at=NULL、password_hash は同一の初期パスワードを BCrypt 化した値（$2a$10$...。ハッシュは 1 回だけ計算して全員に設定）。氏名は姓 20×名 20 の表から連番で決める架空名。</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>初期パスワード</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>全員同じ。値は application-local.properties の kintaiflow.dev.seed-password（または環境変数 KINTAIFLOW_DEV_SEED_PASSWORD）で決まる。設計書・Git・チャットには記載しない（本書にも実際の値は書かない）。</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>入社日 hire_date</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>2016-04-01＋（連番×97 日 mod 3500 日）。人ごとに異なる（範囲は 2016-04-01〜2025-10-23）。例：admin@ 2016-04-01、manager@ 2018-11-27、taro@ 2019-06-09、hanako@ 2019-09-14。</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>部署・上長</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>department_id は V1 の INSERT 順の ID（1=管理部、2=システム開発事業部、3=ソリューション事業部、4=SAP事業部、5=クラウド基盤サービス部）を直接指定する。上長を先に保存して ID を確定させ、その後に部下の manager_id を設定する（自己参照 FK のため）。</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="10" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>3. 初期管理者（BootstrapAdminInitializer）</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>動作条件</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>環境変数 KINTAIFLOW_BOOTSTRAP_ADMIN_EMAIL と KINTAIFLOW_BOOTSTRAP_ADMIN_PASSWORD（Docker Compose では .env の BOOTSTRAP_ADMIN_EMAIL / _PASSWORD）が空でなく、かつ users が 0 件のとき 1 回だけ。DevDataInitializer が先にユーザーを作った場合は何もしない。</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>作成内容</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>email は trim＋小文字化、氏名『システム管理者』、role=ADMIN、department_id=1（管理部）、hire_date は起動日、status=ACTIVE、must_change_password=TRUE（初回ログインでパスワード変更必須。password_changed_at は NULL のまま）。</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>パスワード要件</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>12 文字以上で英字と数字を含む（AuthService#validatePolicy）。満たさない場合は起動を失敗させる（弱い管理者を作らない）。値は設計書に記載しない。</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>部署 ID 1（管理部）が存在することが前提（V1 の INSERT 順に依存）。</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="10" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>4. 開発用の年次有給休暇の初期付与（DevLeaveBalanceInitializer）</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>動作条件</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>seed-password が空でない、かつ leave_balances が 0 件、かつ users が 1 件以上。休暇種別『年次有給休暇』（名前で検索）が無ければ何もしない。</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>作成内容</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>status=ACTIVE の全ユーザーに 1 行ずつ：granted_days=20.0、used_days=0、granted_on＝起動日が属する年度の 4/1（4〜12 月は当年 4/1、1〜3 月は前年 4/1。例：2026 年 10 月の起動なら 2026-04-01）、expires_on＝付与日の 2 年後（LeaveBalanceService#grant。例：2028-04-01）。</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>年度ごとに 4/1 に自動で付与する仕組みではなく、初回の起動時に 1 回作る開発用の固定値（付与日数表の 10〜20 日とは無関係）。年次有給休暇の自動付与 BAT-001 は設計のみで backend には実装が無い。両方を使うと granted_on が異なる別行になり二重に付与されうる。</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="19.5" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>本番</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>seed-password を設定しないため動かない。本番の付与は ONL-017（管理者の手動付与）で行う。</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="10" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>5. 取り扱い上の注意</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>パスワードの扱い</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>初期パスワードの値は設計書・Git・チャット・ログに書かない。application-local.properties は Git 管理外、.env も Git に入れない（.env.example の DEV_SEED_PASSWORD は空欄）。</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="10" t="n"/>
+    </row>
+    <row r="43" ht="48.5" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>本番での禁止</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>本番では kintaiflow.dev.seed-enabled を設定せず（false 扱い）、DEV_SEED_PASSWORD（kintaiflow.dev.seed-password）も空にする。seed-enabled=true かつ seed-password を設定したまま users が空の状態で初回起動すると、全員同じパスワードの架空ユーザー 100 名が作られる（課題 U-5）。seed-enabled を付けない限りは seed-password があっても動かない二重の安全策になった。確認 SQL：SELECT COUNT(*) FROM users WHERE email LIKE '%@example.com';（本番は 0）。</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="10" t="n"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>作り直し</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>開発 DB は backend/db/reset-dev.sql（DROP SCHEMA public CASCADE; CREATE SCHEMA public;）で空に戻して再起動すると、Flyway が V1〜V5 を適用し、開発用ユーザーと年休付与が再び作られる（seed-enabled=true の環境のみ）。本番では実行しない。</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="10" t="n"/>
+    </row>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>依存関係</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>開発用ユーザー・初期管理者は部署 ID 1〜5、開発用年休付与は休暇種別『年次有給休暇』（名前）に依存する。V1 の INSERT 順・名称を変えない。</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="10" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="41">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A39:B39"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1717,1691 +3899,197 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G49"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="120" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>未解決の課題</t>
-        </is>
-      </c>
-      <c r="B2" s="9" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="10" t="n"/>
-    </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>題名</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>影響</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>推奨対応</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>優先度</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>対象テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>C-4</t>
-        </is>
+    </row>
+    <row r="2" ht="63" customHeight="1">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>現状</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Flyway で管理する。backend/src/main/resources/db/migration/ の V1__init_schema.sql（DDL・トリガ・部署と休暇種別の初期データ。DROP は含まない）・V2__seed_holidays.sql（祝日 2026〜2027 年）・V3__seed_holidays_2028.sql（祝日 2028 年）・V4__attendance_breaks.sql（休憩・離席の表）・V5__break_correction_request.sql（休憩・離席修正申請用の列・制約）をアプリ起動時に自動適用する。旧 backend/schema.sql（手動実行・先頭に DROP）は廃止（解消済み C-3）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="106.5" customHeight="1">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>適用済みマイグレーション</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql：9 テーブル・索引・関数 set_updated_at・トリガ・部署 5 件・休暇種別 11 件。V2__seed_holidays.sql：2026〜2027 年の祝日・会社休日 43 件（INSERT … ON CONFLICT (holiday_date) DO NOTHING。DDL なし）。V3__seed_holidays_2028.sql：2028 年の祝日・会社休日 21 件（同じく ON CONFLICT DO NOTHING。DDL なし）。V4__attendance_breaks.sql：attendance_breaks（休憩・日中離席の区間）の追加。部分一意索引 uq_attendance_breaks_open・索引 idx_attendance_breaks_record・トリガ trg_attendance_breaks_updated_at を含む。V5__break_correction_request.sql：requests に corrected_break_kind / corrected_break_start / corrected_break_end（いずれも NULL 可）を追加し、ck_req_type を DROP して BREAK_CORRECTION を許す定義で再作成、ck_req_break_kind を追加。現在の最新版は V5、次に追加する版は V6。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48.5" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>PK 制約名が未指定で命名規約と不統一</t>
+          <t>命名規則</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="63" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>C-5</t>
-        </is>
+          <t>V&lt;連番&gt;__&lt;内容を表す英小文字のスネークケース&gt;.sql。V と連番のあとにアンダースコア 2 つ。連番は 1 から順に増やす整数で、欠番・重複を作らない（既存：V3__seed_holidays_2028.sql、V4__attendance_breaks.sql、V5__break_correction_request.sql。次の例：V6__seed_holidays_2029.sql）。1 ファイル 1 目的（DDL の変更と初期データは分ける）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48.5" customHeight="1">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>業務ルールの CHECK 制約が少ない</t>
+          <t>適用済みの版は変更しない</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="63" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>C-6</t>
-        </is>
+          <t>Flyway は適用済みファイルのチェックサムを検証する。V1〜V5 を編集・改名・削除すると、既存 DB の起動が検証エラーで失敗する。誤りの修正も変更も、新しい版（V6 以降）を追加して行う。開発 DB は reset-dev.sql で作り直すこともできるが、他の環境と食い違うため V1〜V5 の編集には使わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="77.5" customHeight="1">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
+          <t>JPA・接続の設定</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>U-2</t>
-        </is>
+          <t>spring.jpa.hibernate.ddl-auto=validate：起動時に Entity と DB の型・列の整合を検証するだけで、DDL の自動生成・変更はしない。Entity と DB が食い違うと起動に失敗するため、列の追加・変更は Entity の修正と同じ変更で V&lt;n&gt; を追加する。spring.jpa.open-in-view=false：リクエスト全体では EntityManager を開いたままにしない（Controller・View での遅延ロードは不可。Entity は他表を Long の ID で保持し関連は持たないため影響しない。トランザクションは Service の @Transactional 内で完結させる）。spring.flyway.enabled=true。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>上長の自己参照・循環を DB で防げない</t>
+          <t>既存の開発 DB（baseline-on-migrate）</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>users.manager_id は自己参照 FK。manager_id = id や循環（A→B→A）は ONL-014 のアプリ判定のみ。</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>手動 SQL で循環を作ると承認ルートが成立しない。</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>CHECK (manager_id IS NULL OR manager_id &lt;&gt; id) を追加。循環は 10章の再帰 CTE で定期検査。</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="63" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>U-4</t>
-        </is>
+          <t>spring.flyway.baseline-on-migrate=true・baseline-version=1：Flyway の履歴表（flyway_schema_history）が無い既存 DB（旧 schema.sql で作成）を V1 適用済みとして取り込み、V2 以降だけを適用する（空の DB には働かず、V1 から通常どおり適用）。取り込んだ DB には V2〜V5 が順に適用される（V4・V5 も自動適用）。ただし V1 に含まれる新しい列（users の 4 列）は追加されないため、旧 schema.sql の DB は ddl-auto=validate で起動に失敗する。backend/db/reset-dev.sql（DROP SCHEMA public CASCADE; CREATE SCHEMA public;）で作り直す。本番では実行しない。V2・V3 は既存 DB に祝日が登録済みでも ON CONFLICT DO NOTHING で失敗しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>email の小文字化を DB が強制しない</t>
+          <t>適用手順（現行）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>保存時の小文字化はアプリの責務で、DB に CHECK も LOWER(email) の一意索引も無い。アプリを経由しない手動 SQL や将来の別入口では大文字混じりのメールが入り、uq_users_1 では大文字小文字違いの重複を防げない。</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>大文字混じりのメールはログインに一致しなくなる（検索は小文字）。</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>CHECK (email = LOWER(email))（ck_users_email_lower）を追加。事前に 10章『大文字・前後空白を含むメール』が 0 行であることを確認。</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="63" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>D-1</t>
-        </is>
+          <t>①空の DB を作成（運用接続用に ALTER DATABASE ... SET timezone TO 'Asia/Tokyo' を併用。課題 C-6）②アプリ（または docker compose up -d --build）を起動すると Flyway が V1〜V5 を適用（テーブル・索引・関数 set_updated_at・トリガ・部署・休暇種別・祝日 2026〜2028 年・attendance_breaks・requests の休憩離席修正の列）③Hikari の connection-init-sql で JST に固定され、ddl-auto=validate が通ることを確認④開発のみ（kintaiflow.dev.seed-enabled=true の環境）DevDataInitializer が開発用ユーザーを、DevLeaveBalanceInitializer が年休付与を、本番は BootstrapAdminInitializer が初期管理者を作る（『初期データ・開発用シード』）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48.5" customHeight="1">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>departments に UNIQUE が無く、管理機能も無い</t>
+          <t>変更の入れ方</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>部署名の重複を DB が許す。オンライン処理に部署の登録・変更 API が無い（ONL-014 は R のみ）。初期 5 部署は V1__init_schema.sql の INSERT のみ。部署名変更は過去の申請・集計にも現在名で表示される（ONL-007）。</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>部署追加・改名は SQL 直接実行になる。重複部署の混入を防げない。</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>uq_departments_1 (name) を追加。部署管理 ONL の追加を検討（無効化用 is_active 列も）。</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>departments</t>
+          <t>列・制約・索引・初期データの変更は V6__&lt;内容&gt;.sql のように新しいファイルを追加する。本番適用前に件数・重複の確認 SQL（各テーブル詳細設計書 10章）で既存データが新制約を満たすことを確認する。毎年の祝日追加は ONL-016 で行い、新規環境用に同内容を新しい版（例：2029 年分は V6）にも追加する（課題 H-3）。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48.5" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>LT-1</t>
-        </is>
+      <c r="A10" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>leave_types.max_days_rule が NULL 可</t>
+          <t>既存データの移行（email 小文字化）</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>列は NULL 許可で ck_lt_rule も NULL を通す（SQL の CHECK は NULL で真）。KF-BD-005 と ONL-015 では必須（LIMITED / UNLIMITED）。</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>NULL の種別は LIMITED でも UNLIMITED でもなく、ONL-005 の残日数判定が不定になる。</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>NOT NULL 化（既存 11 件は設定済み）。</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>leave_types</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>LT-2</t>
-        </is>
+          <t>既存 DB に大文字混じりのメールがある場合のみ。①重複確認 SELECT LOWER(BTRIM(email)), COUNT(*) FROM users GROUP BY 1 HAVING COUNT(*) &gt; 1;（0 行）②UPDATE users SET email = LOWER(TRIM(email));（ONL-014 導入時の注意。トリガにより updated_at も更新される）。詳細は KF-DD-TBL-01 の運用章。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="92" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>年次有給休暇を名称で特定している</t>
+          <t>保留中の変更案</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>ONL-013 は findByName('年次有給休暇') で年休を判定。名称変更は ONL-015 が E-016 で拒否するが DB は保護しない。表示順の列も無く id 昇順（ONL-021）。</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>SQL 等で改名すると年休判定・年 5 日義務・BAT-001/002 が働かなくなる。</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>code 列（例 ANNUAL_LEAVE）追加、または name 変更を禁止するトリガ。display_order 列の追加を検討。</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>leave_types</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48.5" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>LT-3</t>
-        </is>
+          <t>各詳細設計書 3.4 の推奨 DDL（採否は課題一覧の優先度で決める。採用時は V6 以降で追加）：idx_lb_user 廃止（LB-6）、ck_users_email_lower（U-4）、requests / leave_balances / attendance_records の CHECK、notifications の ck_notif_type・ck_notif_request（N-3）と索引置換（N-2）、holidays の ck_holiday_range（H-1）・種別列（H-2）、attendance_breaks の EXCLUDE 制約（BR-3）、requests の ck_req_kind（BREAK_CORRECTION 対応）・ck_req_break_range（R-2）。解消済みの項目（updated_at トリガ・notifications の type/request_id・uq_leave_balances_1・idx_att_user_date 削除）は V1__init_schema.sql に反映済み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>日数上限（子の看護・介護休暇、介護休業）は leave_balances の付与で管理</t>
+          <t>バックアップ・復元</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>leave_types には上限日数を持たず、LIMITED 種別は管理者の付与（ONL-017）が無いと残 0 日になる。BAT-001 が自動付与するのは年次有給休暇のみ。</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>付与漏れがあると申請時に E-004（残日数不足）となる。運用ルールが DB から読み取れない。</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>default_days（既定付与日数）列の追加、または付与運用手順を運用設計書に明記。</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>leave_types, leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>LB-2</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>残日数の整合 CHECK が無い</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>granted_days &gt; 0、used_days &gt;= 0、used_days &lt;= granted_days、expires_on &gt; granted_on を DB が保証しない。</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>consume/restore のバグや手動更新で used_days が付与を超える・負になる。</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>CHECK 4 本を追加（ck_lb_days, ck_lb_period）。</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>LB-4</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>消化の内訳が残らない</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>consume は FIFO で複数の付与行から引くが、どの行から何日引いたかを記録しない（ONL-013 既知の制約）。</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>取消（restore）時に元の行へ正確に戻せない。監査証跡が無い。</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>leave_balance_usages（request_id, leave_balance_id, days）の追加を検討。</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>LB-5</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>付与・調整の理由を保存する列が無い</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>ONL-017 D-2：note は通知本文に使うだけで DB に保存しない。</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>調整履歴で理由を追えない。</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>note VARCHAR(200) 列の追加（ONL-017 将来課題）。</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="63" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>LB-6</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>idx_lb_user が uq_leave_balances_1 に包含されて冗長</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>uq_leave_balances_1 (user_id, leave_type_id, granted_on) の先頭 2 列が idx_lb_user (user_id, leave_type_id) と同一で、残日数合計・FIFO 消化・付与履歴の検索はどちらでも賄える。</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>書込み時の索引更新とストレージが無駄（影響は小さい）。</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>DROP INDEX idx_lb_user;</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48.5" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>A-2</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>勤怠値の整合 CHECK が無い</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>clock_out &gt;= clock_in、work_minutes &gt;= 0、overtime_minutes &gt;= 0、clock_out があれば clock_in も必須、を DB が保証しない。</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>打刻修正（ONL-010）や手動更新で退勤が出勤より前、負の時間などを保存できる。</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>CHECK を追加（ck_att_time, ck_att_minutes）。</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>attendance_records</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="63" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>A-3</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>日跨ぎ勤務・休憩・修正履歴に非対応</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>ONL-003：日跨ぎ勤務は未対応（前日出勤・未退勤は E-007）。休憩・所定労働時間の列が無く work_minutes の計算規則はアプリ内。ONL-010 の打刻修正は attendance_records を上書きし、修正前の値・修正者を残さない。</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>夜勤・修正の監査ができない。work_minutes の再計算根拠が DB に無い。</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>break_minutes 列、attendance_record_audits（修正履歴）の追加を検討。</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>attendance_records</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="63" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>A-4</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>月次集計は work_date 先頭の索引が無い</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>ONL-018/020 の集計サブクエリは work_date BETWEEN のみで user_id を限定しない。idx は user_id 先頭のため使えず、期間で全件走査になる（300 名×約 22 日≒6,600 行/月、年 75,000 行までは問題なし）。</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>数年分（数十万行）に増えると月次集計が遅くなる。</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>必要になった時点で idx_att_work_date (work_date) を追加（現状は不要）。</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>attendance_records</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="77.5" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>R-2</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>requests の CHECK 不足（期間・段・種別別必須列）</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>start_date &lt;= end_date、current_step の範囲（0=下書き,1,2）、days &gt; 0、LEAVE 時の leave_type_id/unit/days 必須、CLOCK_CORRECTION 時の corrected_clock_in/out 必須、status と submitted_at の対応を DB が保証しない。current_step は NOT NULL だが DEFAULT も無い。</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>手動投入・将来の別入口で矛盾した申請が入る。</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>ck_req_period / ck_req_step / ck_req_days / ck_req_kind を追加（本書 3章の推奨 DDL）。</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="63" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>R-3</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>取下げ・差戻し等の実行日時・実行者を専用列に残せない</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>updated_at はトリガで信頼できるが、取下げ以外の更新でも更新されるため『取下げ日時』とは断定できない。取下げ者は申請者本人のみのため不要だが、承認履歴は approval_steps にのみ存在する。</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>取下げ日時を厳密に出せない（最終更新日時で代用）。</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>必要なら withdrawn_at 列を追加。</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48.5" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>R-4</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>楽観ロック用 version 列が無い</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>@Version を使えず、requests 行の SELECT ... FOR UPDATE ＋ 状態条件付き UPDATE で排他している（ONL-010 決定事項）。</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>現方式で二重承認は防げるが、ロック待ちが発生する。他の更新経路（管理画面等）が増えると漏れやすい。</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>当面は現方式を維持。更新経路が増える時点で version BIGINT NOT NULL DEFAULT 0 を追加。</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="63" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>R-5</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>集計用の索引が無い</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>ONL-018/020 の requests サブクエリは request_type='LEAVE' AND status='APPROVED' AND start_date BETWEEN（user_id 指定なし）で、user_id 先頭の idx_req_* が使えず全件走査（年 5,000 行までは問題なし）。</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>数年分で月次集計が遅くなる可能性。</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>必要になった時点で (status, start_date) の部分索引を追加。</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="48.5" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>R-6</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>承認ルート確定後の上長変更・無効化への追従が無い</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>承認ルート確定後に users.manager_id が変わっても approval_steps.approver_id は変わらない。1段目の上長が INACTIVE になった場合の代理承認は未対応（ONL-005/010）。</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>承認待ちのまま止まる申請が発生しうる。</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>承認者付替えの管理機能（ONL-014 将来課題）。10章 SQL「承認者が無効な待ち」で検出。</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>requests, approval_steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48.5" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>R-7</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>下書き・差戻しの内容を更新する API が無い</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 は提出（再提出）のみで、下書きの内容更新（PUT）は未定義。RETURNED の申請も内容を修正できず、直したい場合は取り下げて新規申請になる。</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>差戻しの目的（修正して再提出）を画面で果たせない。</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>更新 API（PUT /api/requests/{id}）の追加（DRAFT / RETURNED のみ可）。</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="77.5" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>AS-1</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>WITHDRAWN 等の終了申請に WAITING のステップが残る</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>ONL-008 は approval_steps を更新しない。ONL-011/012 の SQL は処理した 1 ステップのみ更新し、他段を更新しない。例：1段目で却下すると 2段目は WAITING のまま。</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps.status = 'WAITING' だけでは「処理待ち」を意味しない。必ず requests.status='PENDING' AND current_step = step_no と併用する（ONL-009 は実施済み）。集計・バッチで誤用しやすい。</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>方針を明文化（現行の維持）。もしくは終端時に未処理ステップを CANCELLED 等へ更新（コード値追加）。</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps, requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="48.5" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>AS-2</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>ck_as_step が 1,2 固定で 3 段以上に拡張できず、整合 CHECK も無い</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>step_no IN (1,2) は固定。status='WAITING' ⇔ acted_at IS NULL、WAITING 以外は acted_at が必須、といった整合を DB は保証しない。</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>承認段数を増やすと DDL 変更が必要。acted_at 欠落データが入りうる。</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>ck_as_step を step_no BETWEEN 1 AND 9 等へ緩和するか現状維持を決定。ck_as_acted を追加。</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="63" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>AS-3</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>再提出で差戻しコメントなどの承認履歴が失われる</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 は再提出時に旧 approval_steps を全て DELETE して作り直す（uq(request_id, step_no) のため INSERT し直す）。差戻しコメント・処理者・処理日時を含む前回の履歴は DB に残らず、ONL-007 の承認履歴には再提出後のステップのみが出る。</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>承認履歴（コメント・処理者）の喪失。監査・紛争時に追えない。</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>approval_histories（ステップ処理の追記専用ログ）を追加するか、再提出ごとに submit_no を持たせる。</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps, requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="48.5" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>AS-4</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>approver_id の索引は 2段目（NULL）検索に最適でない</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>ONL-009 の承認待ち検索は (1段目 approver_id = 自分) OR (2段目 かつ ADMIN) の OR 条件で、idx_as_approver (approver_id, status) だけでは 2段目を絞り込めない。</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>WAITING が累積すると走査が増える（年 10,000 行までは問題なし）。</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>(step_no, status) WHERE status='WAITING' の部分索引を追加。</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="63" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>AS-5</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 規格が存在しない索引 idx_as_request を参照している</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 の deleteByRequestId の備考に『idx_as_request（request_id）を利用』とあるが、V1__init_schema.sql に該当索引は無い。実際は uq_approval_steps_1 (request_id, step_no) の先頭列が使われる（追加索引は不要）。</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>設計書と DDL の不一致（実害なし）。</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 規格の記載を uq_approval_steps_1 に修正する。</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>approval_steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="63" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>H-1</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>祝日は物理削除可で、誤削除・再計算の仕組みが無い</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>ONL-016：祝日は物理削除。削除・追加は以後の申請の日数計算にのみ影響し、作成済み requests.days は再計算しない。2000-2099 の範囲制限は ONL-016 の入力チェックのみで DB に CHECK が無い。</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>日数が祝日の追加漏れ時点の値で確定する。履歴が残らない。</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>祝日の年次一括登録手順（内閣府 CSV 取込）を運用に定義。ck_holiday_range を追加。</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>holidays</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>H-2</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>祝日と会社休日を区別できない</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>KF-DD-003 は「祝日・会社休日」だが種別列が無く name で区別する。</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>会社休日のみ・祝日のみの抽出ができない。</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>kind 列（NATIONAL / COMPANY）追加を検討。</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>holidays</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="77.5" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>N-2</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>通知の保持・削除方針が無く、取得索引も最適でない</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>年 20,000 件増加。ONL-019 は最新 50 件のみ取得し、画面は先頭 5 件。idx_notif_user (user_id, is_read) の is_read を使う SELECT が無く、一覧の ORDER BY created_at DESC, id DESC のソートが残る。月次の重複確認（user_id, type, created_at 範囲）も user_id のみで絞る。</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>数年で行数が増え続ける。1 ユーザーの全通知をソートして上位 50 件を取る無駄が出る。</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>保持 1 年を超える既読通知の削除バッチを追加。索引を (user_id, created_at DESC, id DESC) へ変更。</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="48.5" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>N-3</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>notifications.type の値と request_id の整合を DB が保証しない</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>type は VARCHAR(30) NULL 可で CHECK が無く、値の妥当性と『REQUEST_* は request_id 必須・LEAVE_* は NULL』は NotificationService#notify の検証のみ。</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>手動 SQL・バッチで未知の type や request_id 欠落の通知が入る。</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>ck_notif_type / ck_notif_request を追加（type が NULL の旧データは許容）。旧データを整理できれば type を NOT NULL 化。</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="92" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>N-4</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>BAT-002 規格の通知種別・重複判定が ONL-005 / 019 と不一致（要同期）</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>BAT-002 規格は type="MANDATORY_LEAVE_ALERT"・requestId=null が保存されない前提・message LIKE による重複確認（existsMonthlyByPattern）のままだが、ONL-005 / 019 は NotificationType.LEAVE_ALERT と existsMonthly（user_id, type, 月）を定義。BAT-001 の SQL も type を含まない INSERT のまま。</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>BAT 実装が type を設定しないと type=NULL の通知が作られ、月次重複確認（type 条件）が効かない。</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>BAT-001 は LEAVE_GRANTED、BAT-002 は LEAVE_ALERT で notify し、重複確認は existsMonthly に統一するよう BAT 規格を更新する（担当者が更新中）。</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）の課題：履歴</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="10" t="n"/>
-    </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>題名</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>解消内容</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>根拠（DDL／規格）</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>残る事項</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>対象テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="92" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>C-1</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>updated_at が更新時に自動更新されない</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>V1__init_schema.sql（set_updated_at ＋ trg_*_updated_at）／各 ONL 規格の mapping・SQL</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="77.5" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>C-2</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>application.properties（ONL-002 / ONL-019 の config）</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="106.5" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>C-3</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>V1__init_schema.sql／reset-dev.sql／application.properties（spring.flyway.*）／KF-DD-006</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>全テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="106.5" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>U-1</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>メールアドレスの大文字小文字の扱いが処理間で不一致</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>保存・検索とも trim＋toLowerCase(Locale.ROOT) で正規化（ONL-001 は AuthService#login 内で実施済み。EmailNormalizer クラスは未実装で、ONL-014 実装時に共通化）。ONL-001 は正規化後の完全一致、ONL-014 の重複確認も UPPER() 比較をやめて正規化後の完全一致（uq_users_1 の索引が効く）。既存データは UPDATE users SET email = LOWER(TRIM(email)); で一度だけ移行（運用章）。</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>ONL-001 / ONL-014 規格</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>DB が小文字を強制していない（課題 U-4）。</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="77.5" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>U-3</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>ログイン失敗回数・パスワード変更日などの列が無い</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>users に failed_login_count（INT 既定 0）・locked_until（TIMESTAMP）・must_change_password（BOOLEAN 既定 FALSE）・password_changed_at（TIMESTAMP）を追加（V1）。ONL-001 が 5 回失敗で 30 分ロック（E-017）、ONL-023 がパスワード変更で must_change_password を false にする。</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>V1__init_schema.sql／ONL-001 / ONL-023 規格</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>token_version（トークン失効）は未追加。無効化・ロール変更は発行済み JWT（最大 2 時間）に即時反映されない。管理者によるロック手動解除・サーバー側での mustChangePassword 強制は未実装。</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>users</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="48.5" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>LB-1</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>(user_id, leave_type_id, granted_on) の UNIQUE が無い</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>uq_leave_balances_1 を追加。ONL-017 は UNIQUE 違反を E-013 に変換、BAT-001 の冪等チェックと合わせて二重付与を DB が保証する。</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>V1__init_schema.sql（uq_leave_balances_1）／ONL-017</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>UNIQUE が先頭 2 列を包含するため idx_lb_user が冗長に（課題 LB-6）。</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="48.5" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>LB-3</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>失効日 expires_on の境界判定が処理間で不一致</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>全処理を expires_on &gt;= 基準日（失効日当日までは有効）に統一。ONL-005/007/010/013/017/022 と BAT の判定が一致し、申請時と承認時で残日数がずれない。</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>ONL-005 / 007 / 010 / 013 / 022 規格</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>leave_balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>idx_att_user_date が uq_attendance_records_1 と同一列で冗長</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>idx_att_user_date を削除（uq_attendance_records_1 が同じ検索を担う）。</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>V1__init_schema.sql</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>attendance_records</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="77.5" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>R-1</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>下書き提出・差戻し後の再提出を行う ONL が存在しない</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022（POST /api/requests/{id}/submit）を追加。DRAFT / RETURNED → PENDING。ONL-005 と同じ検証（E-004 / E-005）、LEAVE は days を再計算、旧 approval_steps を全て削除して作り直す（uq(request_id, step_no) 対策にバルク DELETE）、現在の承認者へ REQUEST_SUBMITTED 通知。</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>ONL-022 規格</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>下書きの内容を更新する API（課題 R-7）と、再提出で承認履歴が消える点（課題 AS-3）が残る。</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>requests, approval_steps</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="106.5" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>N-1</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>notifications に type / request_id 列が無い</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>type VARCHAR(30) と request_id BIGINT（FK fk_notifications_request_id → requests）を追加。NotificationService#notify が 4 引数（userId, type, message, requestId）で保存。type は REQUEST_SUBMITTED / APPROVED / RETURNED / REJECTED / WITHDRAWN と LEAVE_GRANTED / LEAVE_ALERT。月次の重複確認は ONL-019 の existsMonthly（user_id, type, 作成日時範囲）。</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>V1__init_schema.sql／ONL-005 / 008 / 010〜012 / 017 / 019 / 022 規格</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>type の CHECK が無い（課題 N-3）。BAT-002 規格が旧仕様のまま（課題 N-4）。</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>上の表は未解決の課題（32 件）。解消済みは 10 件（上の表）。ID は欠番のまま履歴として残す。</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n"/>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="9" t="n"/>
-      <c r="E49" s="9" t="n"/>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="10" t="n"/>
+          <t>BAT-003（設計のみ・backend 未実装）が毎日 pg_dump（プレーン SQL）で 7 世代保存する計画。復元は psql -f。復元後は IDENTITY のシーケンスが最大 id を超えていることを確認する。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A37:G37"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3414,7 +4102,2002 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>未解決の課題</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="10" t="n"/>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>題名</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>影響</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>推奨対応</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>対象テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>C-4</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>PK 制約名が未指定で命名規約と不統一</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="63" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>C-5</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>業務ルールの CHECK 制約が少ない</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="63" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>C-6</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="77.5" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>C-7</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>保存期間 5 年を超えたデータの自動削除・アーカイブが未実装</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>KF-RD-002 §9（決定 6）は勤怠・申請・監査ログの保存期間を 5 年（設定値）とし、BAT-005『監査ログ／履歴の保存期間管理（アーカイブ）』を計画している。現行の backend には削除・アーカイブ処理も保存期間の設定値も無く、業務データは物理削除しない（例外は通知・祝日・再提出時の承認ステップ）。</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>運用開始から 5 年間は影響しない。5 年を超えた後の扱い（残す／消す・退避）の手順が無く、運用者の判断になる。件数は 5 年で 5 表合計（attendance_breaks 約 75 万行を含む）約 120 万行規模で、容量・性能上の問題にはなりにくい。</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>運用開始（2026 年）の 5 年後（2031 年）までに、BAT-005 の設計・実装、または手動の退避 SQL の手順を決める。それまでは『消さずに保持する』方針で運用する（5 年はこの方針の目安）。</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances, attendance_records, requests, approval_steps, attendance_breaks</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>U-2</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>上長の自己参照・循環を DB で防げない</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>users.manager_id は自己参照 FK。manager_id = id や循環（A→B→A）は ONL-014 のアプリ判定のみ。</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>手動 SQL で循環を作ると承認ルートが成立しない。</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>CHECK (manager_id IS NULL OR manager_id &lt;&gt; id) を追加。循環は 10章の再帰 CTE で定期検査。</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="63" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>U-4</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>email の小文字化を DB が強制しない</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>保存時の小文字化はアプリの責務で、DB に CHECK も LOWER(email) の一意索引も無い。アプリを経由しない手動 SQL や将来の別入口では大文字混じりのメールが入り、uq_users_1 では大文字小文字違いの重複を防げない。</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>大文字混じりのメールはログインに一致しなくなる（検索は小文字）。</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>CHECK (email = LOWER(email))（ck_users_email_lower）を追加。事前に 10章『大文字・前後空白を含むメール』が 0 行であることを確認。</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="121" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>U-5</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>開発用シードの実行条件がプロパティの有無だけで、Spring プロファイルで制限していない</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>DevDataInitializer・DevLeaveBalanceInitializer は @Profile を持たず、kintaiflow.dev.seed-password が空でないことだけで動く。この値は application-local.properties（Git 管理外。application.properties が optional で読み込む）または環境変数 KINTAIFLOW_DEV_SEED_PASSWORD（Docker Compose の .env の DEV_SEED_PASSWORD）で設定できる。作成は users が 0 件のとき（年休付与は leave_balances が 0 件のとき）に限る。</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>本番で users が空のまま seed-password を設定して初回起動すると、全員が同じパスワードの架空ユーザー 100 名（admin@example.com は ADMIN）が作られる。</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>本番では DEV_SEED_PASSWORD を空にして初回起動する（運用。.env.example も空欄）。コード側で @Profile の付与や本番での起動拒否を検討する（コード変更のため本書の範囲外）。確認 SQL：users の @example.com が 0 件であること。</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>users, leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="63" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>departments に UNIQUE が無く、管理機能も無い</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>部署名の重複を DB が許す。オンライン処理に部署の登録・変更 API が無い（ONL-014 は R のみ）。初期 5 部署は V1__init_schema.sql の INSERT のみ。部署名変更は過去の申請・集計にも現在名で表示される（ONL-007）。</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>部署追加・改名は SQL 直接実行になる。重複部署の混入を防げない。</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>uq_departments_1 (name) を追加。部署管理 ONL の追加を検討（無効化用 is_active 列も）。</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>departments</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>LT-1</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>leave_types.max_days_rule が NULL 可</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>列は NULL 許可で ck_lt_rule も NULL を通す（SQL の CHECK は NULL で真）。KF-BD-005 と ONL-015 では必須（LIMITED / UNLIMITED）。</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>NULL の種別は LIMITED でも UNLIMITED でもなく、ONL-005 の残日数判定が不定になる。</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>NOT NULL 化（既存 11 件は設定済み）。</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>leave_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48.5" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>LT-2</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>年次有給休暇を名称で特定している</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ONL-013 は findByName('年次有給休暇') で年休を判定。名称変更は ONL-015 が E-016 で拒否するが DB は保護しない。表示順の列も無く id 昇順（ONL-021）。</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SQL 等で改名すると年休判定・年 5 日義務・BAT-001/002 が働かなくなる。</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>code 列（例 ANNUAL_LEAVE）追加、または name 変更を禁止するトリガ。display_order 列の追加を検討。</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>leave_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48.5" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>LT-3</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>日数上限（子の看護・介護休暇、介護休業）は leave_balances の付与で管理</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>leave_types には上限日数を持たず、LIMITED 種別は管理者の付与（ONL-017）が無いと残 0 日になる。BAT-001 が自動付与するのは年次有給休暇のみ。</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>付与漏れがあると申請時に E-004（残日数不足）となる。運用ルールが DB から読み取れない。</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>default_days（既定付与日数）列の追加、または付与運用手順を運用設計書に明記。</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>leave_types, leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>LB-2</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>残日数の整合 CHECK が無い</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>granted_days &gt; 0、used_days &gt;= 0、used_days &lt;= granted_days、expires_on &gt; granted_on を DB が保証しない。</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>consume/restore のバグや手動更新で used_days が付与を超える・負になる。</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>CHECK 4 本を追加（ck_lb_days, ck_lb_period）。</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>LB-4</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>消化の内訳が残らない</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>consume は FIFO で複数の付与行から引くが、どの行から何日引いたかを記録しない（ONL-013 既知の制約）。</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>取消（restore）時に元の行へ正確に戻せない。監査証跡が無い。</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>leave_balance_usages（request_id, leave_balance_id, days）の追加を検討。</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>LB-5</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>付与・調整の理由を保存する列が無い</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>ONL-017 D-2：note は通知本文に使うだけで DB に保存しない。</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>調整履歴で理由を追えない。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>note VARCHAR(200) 列の追加（ONL-017 将来課題）。</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="63" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>LB-6</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>idx_lb_user が uq_leave_balances_1 に包含されて冗長</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>uq_leave_balances_1 (user_id, leave_type_id, granted_on) の先頭 2 列が idx_lb_user (user_id, leave_type_id) と同一で、残日数合計・FIFO 消化・付与履歴の検索はどちらでも賄える。</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>書込み時の索引更新とストレージが無駄（影響は小さい）。</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>DROP INDEX idx_lb_user;</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48.5" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>勤怠値の整合 CHECK が無い</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>clock_out &gt;= clock_in、work_minutes &gt;= 0、overtime_minutes &gt;= 0、clock_out があれば clock_in も必須、を DB が保証しない。</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>打刻修正（ONL-010）や手動更新で退勤が出勤より前、負の時間などを保存できる。</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>CHECK を追加（ck_att_time, ck_att_minutes）。</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>attendance_records</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="106.5" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>A-3</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>日跨ぎ勤務・修正履歴に非対応（休憩・離席は V4 で対応済み）</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>ONL-003：日跨ぎ勤務は未対応（前日出勤・未退勤は E-007）。休憩・離席は V4 の子表 attendance_breaks に区間として記録し、work_minutes は区間を反映して計算するようになった（休憩列・離席列は不要）。所定労働時間の列は無く（480 分はアプリ内の定数）、ONL-010 の打刻修正は attendance_records を上書きし、修正前の値・修正者を残さない。休憩・離席修正（BREAK_CORRECTION）の反映も、区間の修正前の値を残さない。</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>夜勤・修正の監査ができない。work_minutes の再計算根拠は子表の区間と AttendanceCalculator の規則（KF-DD-TBL-10 の 4.4）で、DB は結果の分だけを保持する。</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>attendance_record_audits（修正履歴）の追加を検討。</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>attendance_records</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="63" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>A-4</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>月次集計は work_date 先頭の索引が無い</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>ONL-018/020 の集計サブクエリは work_date BETWEEN のみで user_id を限定しない。idx は user_id 先頭のため使えず、期間で全件走査になる（300 名×約 22 日≒6,600 行/月、年 75,000 行までは問題なし）。</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>数年分（数十万行）に増えると月次集計が遅くなる。</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>必要になった時点で idx_att_work_date (work_date) を追加（現状は不要）。</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>attendance_records</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="106.5" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>R-2</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>requests の CHECK 不足（期間・段・種別別必須列）</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>start_date &lt;= end_date、current_step の範囲（0=下書き,1,2）、days &gt; 0、LEAVE 時の leave_type_id/unit/days 必須、CLOCK_CORRECTION 時の corrected_clock_in/out 必須、BREAK_CORRECTION 時の corrected_break_kind/start/end 必須（開始＜終了・対象日と同じ日付）、status と submitted_at の対応を DB が保証しない。current_step は NOT NULL だが DEFAULT も無い。</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>手動投入・将来の別入口で矛盾した申請が入る。</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>ck_req_period / ck_req_step / ck_req_days / ck_req_kind / ck_req_break_range を追加（本書 3章の推奨 DDL）。</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="63" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>R-3</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>取下げ・差戻し等の実行日時・実行者を専用列に残せない</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>updated_at はトリガで信頼できるが、取下げ以外の更新でも更新されるため『取下げ日時』とは断定できない。取下げ者は申請者本人のみのため不要だが、承認履歴は approval_steps にのみ存在する。</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>取下げ日時を厳密に出せない（最終更新日時で代用）。</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>必要なら withdrawn_at 列を追加。</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48.5" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>R-4</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>楽観ロック用 version 列が無い</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>@Version を使えず、requests 行の SELECT ... FOR UPDATE ＋ 状態条件付き UPDATE で排他している（ONL-010 決定事項）。</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>現方式で二重承認は防げるが、ロック待ちが発生する。他の更新経路（管理画面等）が増えると漏れやすい。</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>当面は現方式を維持。更新経路が増える時点で version BIGINT NOT NULL DEFAULT 0 を追加。</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="63" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>R-5</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>集計用の索引が無い</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>ONL-018/020 の requests サブクエリは request_type='LEAVE' AND status='APPROVED' AND start_date BETWEEN（user_id 指定なし）で、user_id 先頭の idx_req_* が使えず全件走査（年 5,000 行までは問題なし）。</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>数年分で月次集計が遅くなる可能性。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>必要になった時点で (status, start_date) の部分索引を追加。</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48.5" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>R-6</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>承認ルート確定後の上長変更・無効化への追従が無い</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>承認ルート確定後に users.manager_id が変わっても approval_steps.approver_id は変わらない。1段目の上長が INACTIVE になった場合の代理承認は未対応（ONL-005/010）。</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>承認待ちのまま止まる申請が発生しうる。</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>承認者付替えの管理機能（ONL-014 将来課題）。10章 SQL「承認者が無効な待ち」で検出。</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>requests, approval_steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48.5" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>R-7</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>下書き・差戻しの内容を更新する API が無い</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>ONL-022 は提出（再提出）のみで、下書きの内容更新（PUT）は未定義。RETURNED の申請も内容を修正できず、直したい場合は取り下げて新規申請になる。</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>差戻しの目的（修正して再提出）を画面で果たせない。</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>更新 API（PUT /api/requests/{id}）の追加（DRAFT / RETURNED のみ可）。</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="92" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>AS-1</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>WITHDRAWN 等の終了申請に WAITING のステップが残る</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ONL-008 は approval_steps を更新しない。ONL-011/012 の SQL は処理した 1 ステップのみ更新し、他段を更新しない。例：1段目で却下すると 2段目は WAITING のまま。API の応答（ONL-007 の承認履歴）は、PENDING でない申請の WAITING を SKIPPED（処理なし）と表示するが、これは RequestService#displayStatus の表示変換で DB の値は WAITING のまま。</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>approval_steps.status = 'WAITING' だけでは「処理待ち」を意味しない。必ず requests.status='PENDING' AND current_step = step_no と併用する（ONL-009 は実施済み）。集計・バッチで誤用しやすい。</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>方針を明文化（現行の維持。画面上の誤解は SKIPPED 表示で緩和済み）。DB 側でも区別したい場合は、終端時に未処理ステップを CANCELLED 等へ更新（コード値追加）。</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>approval_steps, requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48.5" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>AS-2</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>ck_as_step が 1,2 固定で 3 段以上に拡張できず、整合 CHECK も無い</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>step_no IN (1,2) は固定。status='WAITING' ⇔ acted_at IS NULL、WAITING 以外は acted_at が必須、といった整合を DB は保証しない。</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>承認段数を増やすと DDL 変更が必要。acted_at 欠落データが入りうる。</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>ck_as_step を step_no BETWEEN 1 AND 9 等へ緩和するか現状維持を決定。ck_as_acted を追加。</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>approval_steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="63" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>AS-3</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>再提出で差戻しコメントなどの承認履歴が失われる</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>ONL-022 は再提出時に旧 approval_steps を全て DELETE して作り直す（uq(request_id, step_no) のため INSERT し直す）。差戻しコメント・処理者・処理日時を含む前回の履歴は DB に残らず、ONL-007 の承認履歴には再提出後のステップのみが出る。</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>承認履歴（コメント・処理者）の喪失。監査・紛争時に追えない。</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>approval_histories（ステップ処理の追記専用ログ）を追加するか、再提出ごとに submit_no を持たせる。</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>approval_steps, requests</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48.5" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>AS-4</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>approver_id の索引は 2段目（NULL）検索に最適でない</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>ONL-009 の承認待ち検索は (1段目 approver_id = 自分) OR (2段目 かつ ADMIN) の OR 条件で、idx_as_approver (approver_id, status) だけでは 2段目を絞り込めない。</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>WAITING が累積すると走査が増える（年 10,000 行までは問題なし）。</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>(step_no, status) WHERE status='WAITING' の部分索引を追加。</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>approval_steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="63" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>AS-5</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>ONL-022 規格が存在しない索引 idx_as_request を参照している</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>ONL-022 の deleteByRequestId の備考に『idx_as_request（request_id）を利用』とあるが、V1__init_schema.sql に該当索引は無い。実際は uq_approval_steps_1 (request_id, step_no) の先頭列が使われる（追加索引は不要）。</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>設計書と DDL の不一致（実害なし）。</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>ONL-022 規格の記載を uq_approval_steps_1 に修正する。</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>approval_steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="63" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>H-1</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>祝日は物理削除可で、誤削除・再計算の仕組みが無い</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>ONL-016：祝日は物理削除。削除・追加は以後の申請の日数計算にのみ影響し、作成済み requests.days は再計算しない。2000-2099 の範囲制限は ONL-016 の入力チェックのみで DB に CHECK が無い。</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>日数が祝日の追加漏れ時点の値で確定する。履歴が残らない。</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>祝日の年次一括登録手順（内閣府 CSV 取込）を運用に定義。ck_holiday_range を追加。</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="63" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>H-2</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>祝日と会社休日を区別できない</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>KF-DD-003 は「祝日・会社休日」だが種別列が無く name で区別する（V2 の年末年始は名称『年末年始休暇（会社休日）』）。KF-RD-002 §3.3 は種別（NATIONAL / COMPANY）を持たせる要件だが未実装。</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>会社休日のみ・祝日のみの抽出ができない。</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>kind 列（NATIONAL / COMPANY）追加を検討（V6 以降のマイグレーションで追加。既存 64 件は名称から更新）。</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="77.5" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>H-3</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>祝日の初期データが 2028 年末までで、以降は手動登録が必要</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>V2・V3 は 2026〜2028 年の 64 件のみ。2029 年以降は ONL-016 で登録する運用で、祝日の自動取り込み（内閣府 CSV。KF-RD-002 §3.3）は未実装。</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>2029 年の祝日・年始の会社休日（1/1〜1/3）を登録し忘れると、休暇申請の営業日数が過大に計算される（calcDays は土日と登録済みの祝日だけを除く）。新規構築した環境には ONL-016 の登録分が引き継がれない。</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>毎年 2 月頃に翌年分を ONL-016 で登録し、2028 年中に 2029 年分（特に 1/1〜1/3）を必ず登録する。新規環境用に同内容を V6 以降の INSERT … ON CONFLICT DO NOTHING としても追加する。10章の最終登録日確認を年次点検に含める。</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="77.5" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>N-2</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>通知の保持・削除方針が無く、取得索引も最適でない</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>年 20,000 件増加。ONL-019 は最新 50 件のみ取得し、画面は先頭 5 件。idx_notif_user (user_id, is_read) の is_read を使う SELECT が無く、一覧の ORDER BY created_at DESC, id DESC のソートが残る。月次の重複確認（user_id, type, created_at 範囲）も user_id のみで絞る。</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>数年で行数が増え続ける。1 ユーザーの全通知をソートして上位 50 件を取る無駄が出る。</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>保持 1 年を超える既読通知の削除バッチを追加。索引を (user_id, created_at DESC, id DESC) へ変更。</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48.5" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>N-3</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>notifications.type の値と request_id の整合を DB が保証しない</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>type は VARCHAR(30) NULL 可で CHECK が無く、値の妥当性と『REQUEST_* は request_id 必須・LEAVE_* は NULL』は NotificationService#notify の検証のみ。</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>手動 SQL・バッチで未知の type や request_id 欠落の通知が入る。</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ck_notif_type / ck_notif_request を追加（type が NULL の旧データは許容）。旧データを整理できれば type を NOT NULL 化。</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="92" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>N-4</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>BAT-002 規格の通知種別・重複判定が ONL-005 / 019 と不一致（要同期）</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>BAT-002 規格は type="MANDATORY_LEAVE_ALERT"・requestId=null が保存されない前提・message LIKE による重複確認（existsMonthlyByPattern）のままだが、ONL-005 / 019 は NotificationType.LEAVE_ALERT と existsMonthly（user_id, type, 月）を定義。BAT-001 の SQL も type を含まない INSERT のまま。</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>BAT 実装が type を設定しないと type=NULL の通知が作られ、月次重複確認（type 条件）が効かない。</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>BAT-001 は LEAVE_GRANTED、BAT-002 は LEAVE_ALERT で notify し、重複確認は existsMonthly に統一するよう BAT 規格を更新する（担当者が更新中）。</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="77.5" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>H-4</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>V3（2028 年の祝日）の日付が推算値で、公表値と未照合</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>V3__seed_holidays_2028.sql の日付は祝日法の規則（春分・秋分は天文計算による推算）で求めたもので、内閣府の公表値（毎年 2 月頃に翌年分が公表）との照合は未実施。2028 年は振替休日・国民の休日が無い前提で、全 21 件（国民の祝日 16＋年末年始の会社休日 5）を登録している。</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>公表値と異なる日付（春分の日・秋分の日、制度改正など）が登録されたままだと、休暇申請の営業日数が 1 日ずれる。</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>公表後（2028 年分は 2027 年 2 月頃）に内閣府の一覧と照合し、差異があれば ONL-016 で修正するか、新しい版（V6 以降）で補正する。V3 は適用後に編集しない。</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="77.5" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>BR-1</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>休憩・離席の取消・削除が未実装</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>誤って開始・終了した区間を消す・短くする手段が無い。休憩・離席修正申請（BREAK_CORRECTION）は『区間の追加』と『継続中の同種別の区間の修正』だけで、終了済みの区間は直せない（他の区間との重なりは E-005 で拒否される）。0 分区間（開始＝終了。CHECK が許す）の自動破棄も無い。</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>誤打刻した分が勤務時間から控除され続ける（離席の誤打刻は全て控除）。</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>区間の取消・削除（または終了済みの区間の修正）を行う API／申請種別の追加。0 分区間は自動破棄または CHECK（end_at &gt; start_at）で禁止（ただし終了打刻の直後の押し間違いが 0 分になりうるため、破棄側が望ましい）。</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="63" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>BR-2</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>休憩不足（法定未満）の警告が未実装</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>休憩を打刻した日は打刻合計を控除するため、法定の休憩（6 時間超 45 分・8 時間超 60 分）に満たなくても自動では補わず、警告も出さない。休憩を 1 回も打刻しない日は法定休憩を自動控除する。</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>労働基準法第34条の休憩不足に気付けない。打刻漏れでも法定休憩が控除されない日が出る（休憩を一部だけ打刻した場合）。</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>10章の確認 SQL で日次点検、または打刻・月次表示での警告表示を実装する。</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="92" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>BR-3</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>区間の重なり・範囲外を DB が検査しない</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>同じ勤務日の区間が時間帯で重なること、出勤〜退勤の範囲外にはみ出すことを DB は止めない。継続中の区間が 1 つに限ることだけ部分一意索引で保証している。重なり・範囲は休憩・離席修正（BREAK_CORRECTION）の検証（提出時・最終承認時。E-003/E-005）が守る。打刻（開始・終了）はサーバー時刻で順に積まれるため通常は重ならない。</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>手動 SQL や将来の別入口で重なった区間が入ると、勤務時間の控除が二重になる。</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>EXCLUDE 制約（btree_gist。本書 3章の推奨 DDL）または確認 SQL（10章）での定期点検。</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="92" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>BR-4</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>退勤済み・過去日に継続中の区間が残りうる</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>退勤打刻（ONL-003）は継続中の区間があると E-022 で拒否するが、打刻修正申請の承認（ONL-010 の applyClockCorrection）は継続中の区間を確認せずに clock_out を設定する。また終了を押し忘れたまま日が替わると、過去日の継続中の区間が残る（開始・終了の打刻は本日の行だけが対象）。継続中の区間は勤務時間の計算では無視される。</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>ONL-004 の応答に endAt が null の区間が残る。勤務時間に反映されない（休憩・離席が控除されない）。</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>打刻修正の承認時に継続中の区間を検出して拒否または終了させる。当面は休憩・離席修正申請（同種別の継続中の区間を修正できる）で補う。10章の確認 SQL で検出。</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks, attendance_records</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）の課題：履歴</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="10" t="n"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>題名</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>解消内容</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>根拠（DDL／規格）</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>残る事項</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>対象テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="92" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>updated_at が更新時に自動更新されない</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>V1 の全 9 表（V4 の attendance_breaks にも同様）に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql（set_updated_at ＋ trg_*_updated_at）／各 ONL 規格の mapping・SQL</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="106.5" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>C-2</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>application.properties（ONL-002 / ONL-019 の config）</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="106.5" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>C-3</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql／reset-dev.sql／application.properties（spring.flyway.*）／KF-DD-006</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>全テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="106.5" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>U-1</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>メールアドレスの大文字小文字の扱いが処理間で不一致</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>保存・検索とも trim＋toLowerCase(Locale.ROOT) で正規化（ONL-001 は AuthService#login 内で実施済み。EmailNormalizer クラスは未実装で、ONL-014 実装時に共通化）。ONL-001 は正規化後の完全一致、ONL-014 の重複確認も UPPER() 比較をやめて正規化後の完全一致（uq_users_1 の索引が効く）。既存データは UPDATE users SET email = LOWER(TRIM(email)); で一度だけ移行（運用章）。</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>ONL-001 / ONL-014 規格</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>DB が小文字を強制していない（課題 U-4）。</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="77.5" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>U-3</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>ログイン失敗回数・パスワード変更日などの列が無い</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>users に failed_login_count（INT 既定 0）・locked_until（TIMESTAMP）・must_change_password（BOOLEAN 既定 FALSE）・password_changed_at（TIMESTAMP）を追加（V1）。ONL-001 が 5 回失敗で 30 分ロック（E-017）、ONL-023 がパスワード変更で must_change_password を false にする。</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql／ONL-001 / ONL-023 規格</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>token_version（トークン失効）は未追加。無効化・ロール変更は発行済み JWT（最大 2 時間）に即時反映されない。管理者によるロック手動解除・サーバー側での mustChangePassword 強制は未実装。</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48.5" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>LB-1</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>(user_id, leave_type_id, granted_on) の UNIQUE が無い</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>uq_leave_balances_1 を追加。ONL-017 は UNIQUE 違反を E-013 に変換、BAT-001 の冪等チェックと合わせて二重付与を DB が保証する。</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql（uq_leave_balances_1）／ONL-017</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>UNIQUE が先頭 2 列を包含するため idx_lb_user が冗長に（課題 LB-6）。</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48.5" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>LB-3</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>失効日 expires_on の境界判定が処理間で不一致</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>全処理を expires_on &gt;= 基準日（失効日当日までは有効）に統一。ONL-005/007/010/013/017/022 と BAT の判定が一致し、申請時と承認時で残日数がずれない。</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>ONL-005 / 007 / 010 / 013 / 022 規格</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>idx_att_user_date が uq_attendance_records_1 と同一列で冗長</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>idx_att_user_date を削除（uq_attendance_records_1 が同じ検索を担う）。</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>attendance_records</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="77.5" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>R-1</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>下書き提出・差戻し後の再提出を行う ONL が存在しない</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>ONL-022（POST /api/requests/{id}/submit）を追加。DRAFT / RETURNED → PENDING。ONL-005 と同じ検証（E-004 / E-005）、LEAVE は days を再計算、旧 approval_steps を全て削除して作り直す（uq(request_id, step_no) 対策にバルク DELETE）、現在の承認者へ REQUEST_SUBMITTED 通知。</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>ONL-022 規格</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>下書きの内容を更新する API（課題 R-7）と、再提出で承認履歴が消える点（課題 AS-3）が残る。</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>requests, approval_steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="106.5" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>N-1</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>notifications に type / request_id 列が無い</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>type VARCHAR(30) と request_id BIGINT（FK fk_notifications_request_id → requests）を追加。NotificationService#notify が 4 引数（userId, type, message, requestId）で保存。type は REQUEST_SUBMITTED / APPROVED / RETURNED / REJECTED / WITHDRAWN と LEAVE_GRANTED / LEAVE_ALERT。月次の重複確認は ONL-019 の existsMonthly（user_id, type, 作成日時範囲）。</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql／ONL-005 / 008 / 010〜012 / 017 / 019 / 022 規格</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>type の CHECK が無い（課題 N-3）。BAT-002 規格が旧仕様のまま（課題 N-4）。</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>上の表は未解決の課題（40 件）。解消済みは 10 件（上の表）。ID は欠番のまま履歴として残す。</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A45:G45"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E78"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5377,40 +8060,32 @@
       <c r="G63" s="6" t="inlineStr"/>
       <c r="H63" s="6" t="inlineStr"/>
     </row>
-    <row r="64" ht="19.5" customHeight="1">
+    <row r="64" ht="34" customHeight="1">
       <c r="A64" s="6" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>approval_steps</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>corrected_break_kind</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr"/>
       <c r="H64" s="6" t="inlineStr"/>
     </row>
     <row r="65" ht="34" customHeight="1">
@@ -5419,35 +8094,27 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>approval_steps</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>corrected_break_start</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>FK→requests</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>uq_approval_steps_1</t>
-        </is>
-      </c>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
     </row>
     <row r="66" ht="34" customHeight="1">
       <c r="A66" s="6" t="n">
@@ -5455,31 +8122,27 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>approval_steps</t>
+          <t>requests</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>step_no</t>
+          <t>corrected_break_end</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
       <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>uq_approval_steps_1</t>
-        </is>
-      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67" ht="19.5" customHeight="1">
       <c r="A67" s="6" t="n">
@@ -5492,7 +8155,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>approver_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -5502,18 +8165,22 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr"/>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>FK→users</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr"/>
     </row>
-    <row r="68" ht="19.5" customHeight="1">
+    <row r="68" ht="34" customHeight="1">
       <c r="A68" s="6" t="n">
         <v>67</v>
       </c>
@@ -5524,12 +8191,12 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>request_id</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -5538,10 +8205,18 @@
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>FK→requests</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>uq_approval_steps_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="34" customHeight="1">
       <c r="A69" s="6" t="n">
         <v>68</v>
       </c>
@@ -5552,22 +8227,26 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>step_no</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
       <c r="G69" s="6" t="inlineStr"/>
-      <c r="H69" s="6" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>uq_approval_steps_1</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="19.5" customHeight="1">
       <c r="A70" s="6" t="n">
@@ -5580,12 +8259,12 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>acted_at</t>
+          <t>approver_id</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -5594,7 +8273,11 @@
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
-      <c r="G70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>FK→users</t>
+        </is>
+      </c>
       <c r="H70" s="6" t="inlineStr"/>
     </row>
     <row r="71" ht="19.5" customHeight="1">
@@ -5608,12 +8291,12 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -5621,11 +8304,7 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="F71" s="6" t="inlineStr"/>
       <c r="G71" s="6" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr"/>
     </row>
@@ -5640,24 +8319,20 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr"/>
       <c r="G72" s="6" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr"/>
     </row>
@@ -5667,34 +8342,26 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
+          <t>approval_steps</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>acted_at</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr"/>
     </row>
     <row r="74" ht="19.5" customHeight="1">
@@ -5703,17 +8370,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
+          <t>approval_steps</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>holiday_date</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -5721,13 +8388,13 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr"/>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>uq_holidays_1</t>
-        </is>
-      </c>
+      <c r="H74" s="6" t="inlineStr"/>
     </row>
     <row r="75" ht="19.5" customHeight="1">
       <c r="A75" s="6" t="n">
@@ -5735,17 +8402,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>holidays</t>
+          <t>approval_steps</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -5753,7 +8420,11 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G75" s="6" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr"/>
     </row>
@@ -5768,12 +8439,12 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -5783,10 +8454,14 @@
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr"/>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="H76" s="6" t="inlineStr"/>
     </row>
     <row r="77" ht="19.5" customHeight="1">
@@ -5800,12 +8475,12 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>holiday_date</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -5813,13 +8488,13 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="F77" s="6" t="inlineStr"/>
       <c r="G77" s="6" t="inlineStr"/>
-      <c r="H77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>uq_holidays_1</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="19.5" customHeight="1">
       <c r="A78" s="6" t="n">
@@ -5827,17 +8502,17 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>holidays</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -5845,16 +8520,8 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>IDENTITY</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr"/>
       <c r="H78" s="6" t="inlineStr"/>
     </row>
     <row r="79" ht="19.5" customHeight="1">
@@ -5863,17 +8530,17 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>holidays</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -5881,12 +8548,12 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr"/>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>FK→users</t>
-        </is>
-      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
       <c r="H79" s="6" t="inlineStr"/>
     </row>
     <row r="80" ht="19.5" customHeight="1">
@@ -5895,29 +8562,33 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>holidays</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr"/>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G80" s="6" t="inlineStr"/>
       <c r="H80" s="6" t="inlineStr"/>
     </row>
-    <row r="81" ht="34" customHeight="1">
+    <row r="81" ht="19.5" customHeight="1">
       <c r="A81" s="6" t="n">
         <v>80</v>
       </c>
@@ -5928,7 +8599,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5938,13 +8609,17 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="inlineStr"/>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>FK→requests</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr"/>
@@ -5960,12 +8635,12 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -5974,7 +8649,11 @@
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
-      <c r="G82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>FK→users</t>
+        </is>
+      </c>
       <c r="H82" s="6" t="inlineStr"/>
     </row>
     <row r="83" ht="19.5" customHeight="1">
@@ -5988,28 +8667,24 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>is_read</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr"/>
       <c r="G83" s="6" t="inlineStr"/>
       <c r="H83" s="6" t="inlineStr"/>
     </row>
-    <row r="84" ht="19.5" customHeight="1">
+    <row r="84" ht="34" customHeight="1">
       <c r="A84" s="6" t="n">
         <v>83</v>
       </c>
@@ -6020,25 +8695,25 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>request_id</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr"/>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>FK→requests</t>
+        </is>
+      </c>
       <c r="H84" s="6" t="inlineStr"/>
     </row>
     <row r="85" ht="19.5" customHeight="1">
@@ -6052,12 +8727,12 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(500)</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -6065,31 +8740,339 @@
           <t>不可</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="F85" s="6" t="inlineStr"/>
       <c r="G85" s="6" t="inlineStr"/>
       <c r="H85" s="6" t="inlineStr"/>
     </row>
     <row r="86" ht="19.5" customHeight="1">
-      <c r="A86" s="6" t="inlineStr">
+      <c r="A86" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>is_read</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1">
+      <c r="A87" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88" ht="19.5" customHeight="1">
+      <c r="A88" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="A89" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>IDENTITY</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90" ht="48.5" customHeight="1">
+      <c r="A90" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>attendance_record_id</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>FK→attendance_records</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr"/>
+    </row>
+    <row r="91" ht="19.5" customHeight="1">
+      <c r="A91" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr"/>
+      <c r="G91" s="6" t="inlineStr"/>
+      <c r="H91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="A92" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>start_at</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr"/>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93" ht="19.5" customHeight="1">
+      <c r="A93" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>end_at</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr"/>
+      <c r="H93" s="6" t="inlineStr"/>
+    </row>
+    <row r="94" ht="19.5" customHeight="1">
+      <c r="A94" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="A95" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96" ht="19.5" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>V1__init_schema.sql の自動生成。個別の説明は各テーブル詳細設計書の 2章を参照。</t>
         </is>
       </c>
-      <c r="B86" s="9" t="n"/>
-      <c r="C86" s="9" t="n"/>
-      <c r="D86" s="9" t="n"/>
-      <c r="E86" s="9" t="n"/>
-      <c r="F86" s="9" t="n"/>
-      <c r="G86" s="9" t="n"/>
-      <c r="H86" s="10" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A96:H96"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6103,7 +9086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6140,7 +9123,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="19.5" customHeight="1">
+    <row r="2" ht="23" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -6163,7 +9146,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr"/>
     </row>
-    <row r="3" ht="164.5" customHeight="1">
+    <row r="3" ht="188" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -6186,7 +9169,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr"/>
     </row>
-    <row r="4" ht="92" customHeight="1">
+    <row r="4" ht="113" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2.1</t>
@@ -6208,6 +9191,52 @@
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5" ht="203" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>コード（V1・V2 マイグレーション、JPA Entity、application.properties、DevDataInitializer / BootstrapAdminInitializer / DevLeaveBalanceInitializer）と突合して修正。①V2__seed_holidays.sql（2026〜2027 年の国民の祝日＋年末年始の会社休日 43 件。ON CONFLICT (holiday_date) DO NOTHING）を初期データ・DDL の記述に追加し、毎年の追加運用を明記②新章『初期データ・開発用シード』を追加（開発用ユーザー 100 名・初期管理者・開発用年休付与の条件と内容。パスワード値は記載しない）③開発用ユーザーの入社日の記述を訂正（全員 2024-04-01 ではなく 2016-04-01＋連番×97 日 mod 3500 日）④マイグレーション方針を更新（命名規則・適用済み版を編集しない原則・baseline-on-migrate / ddl-auto=validate / open-in-view=false・V2 追加）⑤保存期間 5 年の保持方針を追加し、自動削除・アーカイブは未実装と明記（課題 C-7）⑥タイムゾーン記述から実在しない hibernate.jdbc.time_zone を削除⑦課題 U-5（開発用シードの実行条件）・H-3（祝日の初期データの期限）を追加。ER 図・CRUD マトリクス・全列一覧は V1 から再生成（変更なし）。</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6" ht="323" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>コード（V3〜V5 マイグレーション、JPA Entity：AttendanceBreak・Request、application-local.properties、DevDataInitializer / DevLeaveBalanceInitializer、AttendanceService / AttendanceCalculator / RequestService / ApprovalService / DepartmentController）と突合して更新。①新表 attendance_breaks（休憩・日中離席の区間。V4。KF-DD-TBL-10）を追加：全 10 テーブルに変更し、ER 図（attendance_records の子表）・CRUD マトリクス・テーブル一覧・命名規約・削除方針（保存期間）・全列一覧・課題一覧（BR-1〜BR-4）に反映②requests に休憩・離席修正申請（BREAK_CORRECTION）用の 3 列（corrected_break_kind / corrected_break_start / corrected_break_end）と制約 ck_req_type（BREAK_CORRECTION を許可）・ck_req_break_kind を追加（V5）③V3__seed_holidays_2028.sql（2028 年の祝日・会社休日 21 件）を初期データに追加し、祝日の初期データを 64 件（2026〜2028 年）に更新。2029 年分の登録が次の運用課題（H-3）、V3 の日付は推算値で公表値と未照合（H-4）④『初期データ・開発用シード』を更新：開発用シードは kintaiflow.dev.seed-enabled=true のときだけ動く（@ConditionalOnProperty。application-local.properties に設定、本番では未設定）。V4・V5 は DDL のみで初期データを持たないことを明記⑤マイグレーション方針を更新：適用済みは V1〜V5、次に追加する版は V6。V4・V5 適用時の注意（V5 は requests の制約を再作成）を追記⑥CRUD マトリクスに ONL-024（休憩・離席の開始）・ONL-025（終了）・ONL-026（部署一覧）を追加し、ONL-003/004/005/010/022 の attendance_breaks 等へのアクセスを反映（ONL-024〜026 の番号は仮）⑦承認ステップの記述を訂正（上長なし・無効の場合は 2段目のみ。表示状態 SKIPPED は API 層の変換で DB の値は不変。KF-DD-TBL-07 参照）⑧課題 A-3・R-2・AS-1・H-2・H-3・C-7 を更新、H-4 を追加。</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6222,7 +9251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6241,7 +9270,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="34" customHeight="1">
+    <row r="2" ht="48.5" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>DBMS</t>
@@ -6249,7 +9278,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>PostgreSQL 18（開発・本番とも）。H2 は使用しない。なお本書の SQL・INSERT 例・確認用 SQL は PostgreSQL 16 上で V1__init_schema.sql に対して実行確認した（PostgreSQL 18 固有機能は使用していない）。</t>
+          <t>PostgreSQL 18（開発・本番とも）。H2 は使用しない。なお本書の SQL・INSERT 例・確認用 SQL は PostgreSQL 16 上で V1〜V5 のマイグレーション（V1__init_schema.sql・V2__seed_holidays.sql・V3__seed_holidays_2028.sql・V4__attendance_breaks.sql・V5__break_correction_request.sql）に対して実行確認した（PostgreSQL 18 固有機能は使用していない）。</t>
         </is>
       </c>
     </row>
@@ -6313,7 +9342,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="63" customHeight="1">
+    <row r="8" ht="77.5" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>トリガ・関数</t>
@@ -6321,11 +9350,11 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>共通関数 set_updated_at()（PL/pgSQL。NEW.updated_at = CURRENT_TIMESTAMP を返す）を、全 9 表の BEFORE UPDATE FOR EACH ROW トリガ trg_&lt;表&gt;_updated_at から呼ぶ（V1__init_schema.sql 末尾）。CURRENT_TIMESTAMP はトランザクション開始時刻のため同一トランザクション内の更新は同じ値になる。値が変わらない UPDATE や updated_at を明示した UPDATE でも上書きする。INSERT では動かない。pg_dump / 復元（COPY）ではトリガは発火しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="63" customHeight="1">
+          <t>共通関数 set_updated_at()（PL/pgSQL。NEW.updated_at = CURRENT_TIMESTAMP を返す）を、全 10 表の BEFORE UPDATE FOR EACH ROW トリガ trg_&lt;表&gt;_updated_at から呼ぶ（関数と 9 表分は V1__init_schema.sql 末尾、attendance_breaks は V4 で作成）。CURRENT_TIMESTAMP はトランザクション開始時刻のため同一トランザクション内の更新は同じ値になる。値が変わらない UPDATE や updated_at を明示した UPDATE でも上書きする。INSERT では動かない。pg_dump / 復元（COPY）ではトリガは発火しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="77.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>タイムゾーン</t>
@@ -6333,11 +9362,11 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>列型は TIMESTAMP（タイムゾーンなし）で、アプリが Asia/Tokyo の壁時計時刻を書き込む。DEFAULT CURRENT_TIMESTAMP とトリガの値は DB セッションの TimeZone で決まるため、アプリ接続は spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo'（＋ hibernate.jdbc.time_zone=Asia/Tokyo）で JST に固定する（解消済み C-2）。Hikari 以外の接続（psql・復元・BI）は固定されない（課題 C-6）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
+          <t>列型は TIMESTAMP（タイムゾーンなし）で、アプリが Asia/Tokyo の壁時計時刻を書き込む。DEFAULT CURRENT_TIMESTAMP とトリガの値は DB セッションの TimeZone で決まるため、アプリ接続は spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で JST に固定する（hibernate.jdbc.time_zone は設定していない。業務時刻は Asia/Tokyo 固定の Clock から LocalDateTime で取得する。Docker は ENV TZ=Asia/Tokyo。解消済み C-2）。Hikari 以外の接続（psql・復元・BI）は固定されない（課題 C-6）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="63" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>スキーマ管理</t>
@@ -6345,11 +9374,11 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Flyway（backend/src/main/resources/db/migration/V&lt;連番&gt;__&lt;内容&gt;.sql）がアプリ起動時にスキーマを作成・更新する。アプリは spring.jpa.hibernate.ddl-auto=validate で Entity との整合を起動時に検証する（詳細は『マイグレーション方針』）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
+          <t>Flyway（backend/src/main/resources/db/migration/V&lt;連番&gt;__&lt;内容&gt;.sql）がアプリ起動時にスキーマを作成・更新する。アプリは spring.jpa.hibernate.ddl-auto=validate で Entity との整合を起動時に検証し、spring.jpa.open-in-view=false とする。既存 DB の取り込みは spring.flyway.baseline-on-migrate=true・baseline-version=1（詳細は『マイグレーション方針』）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="63" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>DDL</t>
@@ -6357,31 +9386,43 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>backend/src/main/resources/db/migration/V1__init_schema.sql（本書および KF-DD-TBL-01〜09 の列・制約・索引は同ファイルから自動生成）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
+          <t>backend/src/main/resources/db/migration の V1__init_schema.sql（9 テーブル・索引・関数・トリガ。部署 5 件・休暇種別 11 件の初期データを含む）、V4__attendance_breaks.sql（attendance_breaks の追加）、V5__break_correction_request.sql（requests へ休憩・離席修正の 3 列と制約を追加）。本書および KF-DD-TBL-01〜10 の列・制約・索引はこれらから自動生成している。V2・V3 は祝日の初期データのみ（DDL なし）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="63" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>構成</t>
+          <t>初期データ</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>テーブル 9・FK 11（users 自己参照 1 を含む）・UNIQUE 制約 6・CHECK 制約 8・追加索引（CREATE INDEX）7・トリガ 9（関数 set_updated_at 1）。</t>
+          <t>マスタ（V1：部署・休暇種別）と祝日（V2：2026〜2027 年 43 件、V3：2028 年 21 件。計 64 件）は Flyway が投入する（V4・V5 は DDL のみで初期データなし）。ユーザー・開発用の年休付与は SQL ではなくアプリ起動時の初期化処理（DevDataInitializer / BootstrapAdminInitializer / DevLeaveBalanceInitializer）が作り、開発用の 2 つは kintaiflow.dev.seed-enabled=true のときだけ動く。詳細は『初期データ』『初期データ・開発用シード』シート。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>構成</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>テーブル 10・FK 12（users 自己参照 1 を含む）・UNIQUE 制約 6・CHECK 制約 11・追加索引（CREATE INDEX）9・トリガ 10（関数 set_updated_at 1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>詳細設計書</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>テーブル別に KF-DD-TBL-01〜09（1 テーブル 1 ファイル）。列定義・制約・索引とクエリの対応・状態遷移・アクセスパターン・排他・データ例・運用・既知課題・確認 SQL を記載。</t>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>テーブル別に KF-DD-TBL-01〜10（1 テーブル 1 ファイル）。列定義・制約・索引とクエリの対応・状態遷移・アクセスパターン・排他・データ例・運用・既知課題・確認 SQL を記載。</t>
         </is>
       </c>
     </row>
@@ -6398,7 +9439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6573,7 +9614,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="48.5" customHeight="1">
       <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
@@ -6604,7 +9645,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>物理削除しない（付与期間満了後3年以上保存）</t>
+          <t>物理削除しない（付与期間満了後3年以上保存。5年超の自動削除・退避は未実装）</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -6644,7 +9685,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>物理削除しない（5年目安）</t>
+          <t>物理削除しない（5年目安。5年超の自動削除・退避は未実装）</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -6653,7 +9694,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19.5" customHeight="1">
+    <row r="7" ht="48.5" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
@@ -6669,7 +9710,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>休暇申請・打刻修正申請</t>
+          <t>休暇申請・打刻修正申請・休憩離席修正申請（V5 で BREAK_CORRECTION を追加）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -6684,7 +9725,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>物理削除しない（5年目安）</t>
+          <t>物理削除しない（5年目安。5年超の自動削除・退避は未実装）</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -6693,7 +9734,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="48.5" customHeight="1">
+    <row r="8" ht="63" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
@@ -6724,7 +9765,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>物理削除しない（申請と同期間。例外：ONL-022 の再提出で当該申請の旧ステップを削除して作り直す）</t>
+          <t>物理削除しない（申請と同期間。5年超の自動削除・退避は未実装。例外：ONL-022 の再提出で当該申請の旧ステップを削除して作り直す）</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -6733,7 +9774,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
@@ -6764,7 +9805,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>物理削除可（ONL-016）</t>
+          <t>物理削除可（ONL-016）。初期データは V2・V3 の 2026〜2028 年 64 件</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -6804,7 +9845,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>物理削除可・方針未決（推奨：既読1年経過で削除）</t>
+          <t>物理削除可・方針未決（推奨：既読1年経過で削除。自動削除は未実装）</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -6813,23 +9854,63 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="48.5" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>休憩・離席</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>休憩・日中離席の区間（1 勤務日に複数。V4 で追加）</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>〜150,000</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>約 75 万行</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>物理削除しない（5年目安。5年超の自動削除・退避は未実装。区間の取消・削除機能も無い）</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>KF-DD-TBL-10_attendance_breaks_休憩・離席_テーブル詳細設計書.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>想定件数/年は従来の KF-DD-003 の値（leave_types は件数、departments/users/holidays は 1 年間のマスタ件数）。5 年後の目安は年間増加分の単純な 5 年累計（users は在籍者数の見込み）。</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="10" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:H12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6843,7 +9924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:T2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6868,10 +9949,11 @@
     <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>ER 図（9 テーブル・PK/FK・カーディナリティ付き）</t>
+          <t>ER 図（10 テーブル・PK/FK・カーディナリティ付き）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -6911,7 +9993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:L39"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6926,8 +10008,10 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
@@ -6944,7 +10028,8 @@
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="9" t="n"/>
       <c r="K2" s="9" t="n"/>
-      <c r="L2" s="10" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="M2" s="10" t="n"/>
     </row>
     <row r="3" ht="48.5" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -7014,6 +10099,12 @@
         <is>
           <t>notifications
 通知</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>attendance_breaks
+休憩・離席</t>
         </is>
       </c>
     </row>
@@ -7046,6 +10137,7 @@
       <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -7076,6 +10168,7 @@
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" s="6" t="inlineStr"/>
       <c r="L5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -7106,6 +10199,11 @@
       <c r="J6" s="6" t="inlineStr"/>
       <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -7136,6 +10234,11 @@
       <c r="J7" s="6" t="inlineStr"/>
       <c r="K7" s="6" t="inlineStr"/>
       <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -7169,7 +10272,11 @@
           <t>R</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
           <t>C/R/U</t>
@@ -7188,6 +10295,11 @@
       <c r="L8" s="13" t="inlineStr">
         <is>
           <t>C</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
     </row>
@@ -7224,6 +10336,7 @@
       <c r="J9" s="6" t="inlineStr"/>
       <c r="K9" s="6" t="inlineStr"/>
       <c r="L9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -7274,6 +10387,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr"/>
       <c r="L10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -7316,6 +10430,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="M11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="19.5" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -7358,6 +10473,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr"/>
       <c r="L12" s="6" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -7410,6 +10526,11 @@
       <c r="L13" s="13" t="inlineStr">
         <is>
           <t>C</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>C/R/U</t>
         </is>
       </c>
     </row>
@@ -7454,6 +10575,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="M14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="19.5" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -7496,6 +10618,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="M15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -7538,6 +10661,7 @@
       <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -7572,6 +10696,7 @@
       <c r="J17" s="6" t="inlineStr"/>
       <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -7602,6 +10727,7 @@
       <c r="J18" s="6" t="inlineStr"/>
       <c r="K18" s="6" t="inlineStr"/>
       <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -7632,6 +10758,7 @@
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -7674,6 +10801,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="M20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -7716,6 +10844,7 @@
       <c r="J21" s="6" t="inlineStr"/>
       <c r="K21" s="6" t="inlineStr"/>
       <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -7746,6 +10875,7 @@
           <t>R/U</t>
         </is>
       </c>
+      <c r="M22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="19.5" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -7788,6 +10918,7 @@
       <c r="J23" s="6" t="inlineStr"/>
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -7818,6 +10949,7 @@
       <c r="J24" s="6" t="inlineStr"/>
       <c r="K24" s="6" t="inlineStr"/>
       <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="19.5" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -7851,7 +10983,11 @@
           <t>R</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
           <t>R/U</t>
@@ -7870,6 +11006,11 @@
       <c r="L25" s="13" t="inlineStr">
         <is>
           <t>C</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
     </row>
@@ -7902,456 +11043,583 @@
       <c r="J26" s="6" t="inlineStr"/>
       <c r="K26" s="6" t="inlineStr"/>
       <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-024</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>年次有給休暇 自動付与</t>
+          <t>休憩・離席の開始</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
+          <t>ONL</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>C/R</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="6" t="inlineStr"/>
       <c r="J27" s="6" t="inlineStr"/>
       <c r="K27" s="6" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="13" t="inlineStr">
+        <is>
+          <t>C/R</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>BAT-002</t>
+          <t>ONL-025</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>年5日取得義務アラート</t>
+          <t>休憩・離席の終了</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>BAT</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
+          <t>ONL</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr"/>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I28" s="6" t="inlineStr"/>
       <c r="J28" s="6" t="inlineStr"/>
       <c r="K28" s="6" t="inlineStr"/>
-      <c r="L28" s="13" t="inlineStr">
+      <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="12" t="inlineStr">
+        <is>
+          <t>R/U</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>ONL-026</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>部署一覧取得</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>ONL</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>BAT-001</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>年次有給休暇 自動付与</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>C/R</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>年5日取得義務アラート</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>C/R</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>BAT</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="I32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="K32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L29" s="14" t="inlineStr">
+      <c r="L32" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="16" t="inlineStr"/>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>集計：C 登録する処理数</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr"/>
-      <c r="D30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="16" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="16" t="inlineStr"/>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>集計：R 参照する処理数</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr"/>
-      <c r="D31" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="G31" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="H31" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="J31" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="K31" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L31" s="16" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="16" t="inlineStr"/>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>集計：U 更新する処理数</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr"/>
-      <c r="D32" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I32" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J32" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K32" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="16" t="n">
-        <v>1</v>
+      <c r="M32" s="14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="16" t="inlineStr"/>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>集計：D 削除する処理数</t>
+          <t>集計：C 登録する処理数</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr"/>
       <c r="D33" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="16" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="M33" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="16" t="inlineStr"/>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>集計：R 参照する処理数</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr"/>
+      <c r="D34" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J34" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M34" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="16" t="inlineStr"/>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>集計：U 更新する処理数</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr"/>
+      <c r="D35" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="16" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>凡例：C=登録（INSERT）／R=参照（SELECT。FOR UPDATE による行ロックを含む）／U=更新（UPDATE）／D=削除（DELETE）。色は D＞C＞U＞R の優先で表示。* の付いた操作は、規格の『使用テーブル（tables）』欄に記載が無く、規格の SQL 欄にのみ現れるもの（下の突合結果を参照）。BAT-003 は pg_dump による全テーブルの読取（R）。</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="9" t="n"/>
-      <c r="L34" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>CRUD 突合結果（規格 tables と SQL 欄の差異。矛盾ではなく tables 欄の記載漏れ）</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="10" t="n"/>
-    </row>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>テーブル</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>規格 tables の記載</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>SQL 欄から読み取れる操作</t>
-        </is>
-      </c>
+      <c r="F35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="16" t="inlineStr"/>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>集計：D 削除する処理数</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr"/>
+      <c r="D36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="63" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>凡例：C=登録（INSERT）／R=参照（SELECT。FOR UPDATE による行ロックを含む）／U=更新（UPDATE）／D=削除（DELETE）。色は D＞C＞U＞R の優先で表示。* の付いた操作は、規格の『使用テーブル（tables）』欄に記載が無く、規格の SQL 欄にのみ現れるもの（下の突合結果を参照）。BAT-003 は pg_dump による全テーブルの読取（R）。ONL-024〜026（休憩・離席の開始・終了、部署一覧）は 2026/10/05 にコードから追加した処理で、番号は仮（KF-DD-001 の採番に合わせて見直す）。ONL-003/004/005/010/022 の attendance_breaks・attendance_records へのアクセスは、休憩・離席の導入（V4）と休憩・離席修正申請（V5）に伴う追加分で、規格 JSON（ONL-001〜023）の tables 欄ではなく本書の生成元で補っている。</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
       <c r="G37" s="9" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>判断</t>
-        </is>
-      </c>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="9" t="n"/>
-      <c r="L37" s="10" t="n"/>
-    </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>leave_types</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>記載なし</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>consume 内で種別を読む（参考記載）。R を追記推奨</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
-      <c r="L38" s="10" t="n"/>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>ONL-017</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>notifications</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>SQL 欄に INSERT なし（mapping と methods に notify 呼出しあり）</t>
-        </is>
-      </c>
+      <c r="L37" s="9" t="n"/>
+      <c r="M37" s="10" t="n"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>CRUD 突合結果（規格 tables と SQL 欄の差異。矛盾ではなく tables 欄の記載漏れ）</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
       <c r="G39" s="9" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>tables 欄が正。SQL 欄に NotificationService#notify の INSERT を追記推奨</t>
-        </is>
-      </c>
+      <c r="H39" s="9" t="n"/>
+      <c r="I39" s="9" t="n"/>
       <c r="J39" s="9" t="n"/>
       <c r="K39" s="9" t="n"/>
-      <c r="L39" s="10" t="n"/>
+      <c r="L39" s="9" t="n"/>
+      <c r="M39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="19.5" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>テーブル</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>規格 tables の記載</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>SQL 欄から読み取れる操作</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="5" t="n"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>leave_types</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>consume 内で種別を読む（参考記載）。R を追記推奨</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="10" t="n"/>
+      <c r="M41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>ONL-017</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>SQL 欄に INSERT なし（mapping と methods に notify 呼出しあり）</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>tables 欄が正。SQL 欄に NotificationService#notify の INSERT を追記推奨</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="I42:L42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -8534,7 +11802,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
+    <row r="9" ht="48.5" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>UNIQUE 制約</t>
@@ -8552,11 +11820,11 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>連番方式（列名が分からない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19.5" customHeight="1">
+          <t>連番方式（列名が分からない）。V4 の部分一意索引（制約ではなく CREATE UNIQUE INDEX … WHERE）は uq_attendance_breaks_open と意味のある名前</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t>CHECK 制約</t>
@@ -8569,16 +11837,16 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>ck_users_role, ck_lt_rule, ck_req_status, ck_as_step</t>
+          <t>ck_users_role, ck_lt_rule, ck_req_status, ck_as_step, ck_req_break_kind, ck_attendance_breaks_kind</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>略称が表ごとに不統一（users は表名、他は略号）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
+          <t>略称が表ごとに不統一（users・attendance_breaks は表名、他は略号。V4 の attendance_breaks は表名どおり）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48.5" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t>索引</t>
@@ -8591,12 +11859,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>idx_users_manager, idx_lb_user, idx_req_user, idx_as_approver, idx_notif_user</t>
+          <t>idx_users_manager, idx_lb_user, idx_req_user, idx_as_approver, idx_notif_user, idx_attendance_breaks_record</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>略称が不統一。新規は idx_&lt;表&gt;_&lt;対象&gt; を推奨</t>
+          <t>略称が不統一。新規は idx_&lt;表&gt;_&lt;対象&gt; を推奨（V4 の idx_attendance_breaks_record は推奨どおり）。部分一意索引は uq_ 接頭辞（uq_attendance_breaks_open）</t>
         </is>
       </c>
     </row>
@@ -8899,7 +12167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8988,11 +12256,11 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>物理削除しない（付与期間満了後3年以上保存）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
+          <t>物理削除しない（付与期間満了後3年以上保存。5年超の自動削除・退避は未実装）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
           <t>attendance_records</t>
@@ -9005,11 +12273,11 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>物理削除しない（5年目安）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19.5" customHeight="1">
+          <t>物理削除しない（5年目安。5年超の自動削除・退避は未実装）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>requests</t>
@@ -9022,7 +12290,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>物理削除しない（5年目安）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
+          <t>物理削除しない（5年目安。5年超の自動削除・退避は未実装）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
         </is>
       </c>
     </row>
@@ -9039,11 +12307,11 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>物理削除しない（申請と同期間。例外：ONL-022 の再提出で当該申請の旧ステップを削除して作り直す）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="19.5" customHeight="1">
+          <t>物理削除しない（申請と同期間。5年超の自動削除・退避は未実装。例外：ONL-022 の再提出で当該申請の旧ステップを削除して作り直す）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>holidays</t>
@@ -9056,7 +12324,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>物理削除可（ONL-016）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
+          <t>物理削除可（ONL-016）。初期データは V2・V3 の 2026〜2028 年 64 件。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
         </is>
       </c>
     </row>
@@ -9073,22 +12341,213 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>物理削除可・方針未決（推奨：既読1年経過で削除）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="19.5" customHeight="1">
+          <t>物理削除可・方針未決（推奨：既読1年経過で削除。自動削除は未実装）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>物理削除しない</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>物理削除しない（5年目安。5年超の自動削除・退避は未実装。区間の取消・削除機能も無い）。FK は ON DELETE 未指定（NO ACTION＝RESTRICT 相当）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19.5" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>全 FK は ON DELETE 未指定。親を削除すると子が存在する限り FK 違反（23503）になるため、誤削除が連鎖しない。CASCADE は使わない。</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="10" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="10" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>データ保持方針（保存期間 5 年）と実装状況</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>保存期間（方針）</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>根拠／自動削除・アーカイブの実装状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>attendance_records</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>5 年（目安。物理削除しない）</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>根拠：KF-RD-002 §9 決定 6（勤怠・申請・監査ログは 5 年）、労働基準法第 109 条（出勤簿 5 年）。5 年超の自動削除・アーカイブ：未実装（KF-RD-002 の BAT-005 は計画のみ。課題 C-7）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>requests</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>5 年（目安。物理削除しない）</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>根拠：同上。未実装（課題 C-7）。終了状態の申請も履歴として残す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>approval_steps</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>requests と同じ期間</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>承認履歴のため requests と同期間。未実装（課題 C-7）。例外：ONL-022 の再提出は当該申請の旧ステップを削除して作り直す（課題 AS-3）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>leave_balances</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>付与期間満了後 3 年以上（運用は 5 年目安）</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>根拠：労働基準法施行規則第 24 条の 7（年次有給休暇管理簿）。5 年超の退避：未実装（課題 C-7）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>5 年（目安。物理削除しない）</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>親の attendance_records と同じ。根拠：同上。5 年超の自動削除・アーカイブ：未実装（課題 C-7）。区間の取消・削除の機能も無い（課題 BR-1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>users / departments / leave_types</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>期限なし（物理削除しない）</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>退職は status=INACTIVE。個人情報の消去・マスキング手順は未定義。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>holidays</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>期限なし（過去年も残す）</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>営業日数の再現性のため。誤登録は ONL-016 で削除できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>notifications</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>方針未決（推奨：既読 1 年経過で削除）</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>自動削除は未実装（課題 N-2）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48.5" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>5 年を超えたデータの自動削除・アーカイブ、および保存期間の設定値化（KF-RD-002 §9 決定 6）は未実装で、backend に削除・退避の処理も設定項目も無い。当面は『消さずに保持する』運用で、運用開始（2026 年）から 5 年後（2031 年）までに BAT-005 の設計・実装または手動の退避手順を決める（課題 C-7）。なお BAT-001〜003 も設計のみで backend には実装が無い。</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A11:C11"/>
+  <mergeCells count="3">
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A14:C14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
